--- a/Templates/Tables/ValueInfo/T_ValTable.xlsx
+++ b/Templates/Tables/ValueInfo/T_ValTable.xlsx
@@ -7,11 +7,6 @@
   </sheets>
   <definedNames/>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataSignature="AMtx7mgqXo6rdhRj2rJ90wPN1rMvY2Uc+Q=="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -39,7 +34,7 @@
     <t>광고 딜레이</t>
   </si>
   <si>
-    <t>DELTA_T_ADS</t>
+    <t>DELTA_TIME_ADS</t>
   </si>
   <si>
     <t>광고 시간 간격</t>
@@ -93,22 +88,10 @@
     <t>경고 팝업 버튼 수직 간격</t>
   </si>
   <si>
-    <t>OFFSET_V_ALERT_P_BG</t>
-  </si>
-  <si>
-    <t>경고 팝업 배경 수직 간격</t>
-  </si>
-  <si>
     <t>OFFSET_H_ALERT_P_BTN</t>
   </si>
   <si>
     <t>경고 팝업 버튼 수평 간격</t>
-  </si>
-  <si>
-    <t>OFFSET_H_ALERT_P_BG</t>
-  </si>
-  <si>
-    <t>경고 팝업 배경 수평 간격</t>
   </si>
   <si>
     <t>EXTRA_OFFSET_V_ALERT_P_TITLE</t>
@@ -128,12 +111,24 @@
   <si>
     <t>경고 팝업 버튼 추가 수직 간격</t>
   </si>
+  <si>
+    <t>OFFSET_V_ALERT_P_BG</t>
+  </si>
+  <si>
+    <t>경고 팝업 배경 수직 간격</t>
+  </si>
+  <si>
+    <t>OFFSET_H_ALERT_P_BG</t>
+  </si>
+  <si>
+    <t>경고 팝업 배경 수평 간격</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="2">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -143,14 +138,6 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -166,7 +153,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border/>
     <border>
       <left style="thin">
@@ -182,22 +169,9 @@
       </top>
     </border>
     <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
     </border>
     <border>
       <left style="thin">
@@ -212,36 +186,21 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -534,577 +493,615 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
-      <c r="Z2" s="4"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>0.0</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>10.0</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>2.0</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="7"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>0.0</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>6.0</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>1.0</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="7"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>0.0</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>0.0</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>1.0</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="7"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>0.0</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>60.0</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>1.0</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="7"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>0.0</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>60.0</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>1.0</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="7"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>0.0</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>60.0</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>1.0</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="7"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>0.0</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>60.0</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>1.0</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="7"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>0.0</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>70.0</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>2.0</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="7"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>0.0</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>45.0</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>2.0</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="7"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>0.0</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>45.0</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>2.0</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
-      <c r="X12" s="6"/>
-      <c r="Y12" s="6"/>
-      <c r="Z12" s="9"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>0.0</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="C14" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="C15" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="C16" s="5">
         <v>45.0</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D16" s="5">
         <v>2.0</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="6"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="7"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="6">
+      <c r="E16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="7">
         <v>0.0</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C17" s="7">
         <v>145.0</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D17" s="7">
         <v>2.0</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-      <c r="V14" s="6"/>
-      <c r="W14" s="6"/>
-      <c r="X14" s="6"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="7"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="D15" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
-      <c r="X15" s="6"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="7"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="C16" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="D16" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
-      <c r="T16" s="6"/>
-      <c r="U16" s="6"/>
-      <c r="V16" s="6"/>
-      <c r="W16" s="6"/>
-      <c r="X16" s="6"/>
-      <c r="Y16" s="6"/>
-      <c r="Z16" s="7"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="11">
-        <v>0.0</v>
-      </c>
-      <c r="C17" s="11">
-        <v>15.0</v>
-      </c>
-      <c r="D17" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="11"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="11"/>
-      <c r="Z17" s="12"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="1"/>
@@ -6533,60 +6530,8 @@
       <c r="X220" s="1"/>
       <c r="Y220" s="1"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="1"/>
-      <c r="B221" s="1"/>
-      <c r="C221" s="1"/>
-      <c r="D221" s="1"/>
-      <c r="E221" s="1"/>
-      <c r="F221" s="1"/>
-      <c r="G221" s="1"/>
-      <c r="H221" s="1"/>
-      <c r="I221" s="1"/>
-      <c r="J221" s="1"/>
-      <c r="K221" s="1"/>
-      <c r="L221" s="1"/>
-      <c r="M221" s="1"/>
-      <c r="N221" s="1"/>
-      <c r="O221" s="1"/>
-      <c r="P221" s="1"/>
-      <c r="Q221" s="1"/>
-      <c r="R221" s="1"/>
-      <c r="S221" s="1"/>
-      <c r="T221" s="1"/>
-      <c r="U221" s="1"/>
-      <c r="V221" s="1"/>
-      <c r="W221" s="1"/>
-      <c r="X221" s="1"/>
-      <c r="Y221" s="1"/>
-    </row>
-    <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="1"/>
-      <c r="B222" s="1"/>
-      <c r="C222" s="1"/>
-      <c r="D222" s="1"/>
-      <c r="E222" s="1"/>
-      <c r="F222" s="1"/>
-      <c r="G222" s="1"/>
-      <c r="H222" s="1"/>
-      <c r="I222" s="1"/>
-      <c r="J222" s="1"/>
-      <c r="K222" s="1"/>
-      <c r="L222" s="1"/>
-      <c r="M222" s="1"/>
-      <c r="N222" s="1"/>
-      <c r="O222" s="1"/>
-      <c r="P222" s="1"/>
-      <c r="Q222" s="1"/>
-      <c r="R222" s="1"/>
-      <c r="S222" s="1"/>
-      <c r="T222" s="1"/>
-      <c r="U222" s="1"/>
-      <c r="V222" s="1"/>
-      <c r="W222" s="1"/>
-      <c r="X222" s="1"/>
-      <c r="Y222" s="1"/>
-    </row>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
     <row r="223" ht="15.75" customHeight="1"/>
     <row r="224" ht="15.75" customHeight="1"/>
     <row r="225" ht="15.75" customHeight="1"/>
@@ -7365,8 +7310,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/ValueInfo/T_ValTable.xlsx
+++ b/Templates/Tables/ValueInfo/T_ValTable.xlsx
@@ -420,7 +420,7 @@
     <col customWidth="1" min="6" max="6" width="14.43"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -457,7 +457,7 @@
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -494,7 +494,7 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -531,7 +531,7 @@
       <c r="X3" s="5"/>
       <c r="Y3" s="5"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -568,7 +568,7 @@
       <c r="X4" s="5"/>
       <c r="Y4" s="5"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -605,7 +605,7 @@
       <c r="X5" s="5"/>
       <c r="Y5" s="5"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
@@ -642,7 +642,7 @@
       <c r="X6" s="5"/>
       <c r="Y6" s="5"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
@@ -679,7 +679,7 @@
       <c r="X7" s="5"/>
       <c r="Y7" s="5"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
@@ -716,7 +716,7 @@
       <c r="X8" s="5"/>
       <c r="Y8" s="5"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>19</v>
       </c>
@@ -753,7 +753,7 @@
       <c r="X9" s="5"/>
       <c r="Y9" s="5"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>21</v>
       </c>
@@ -790,7 +790,7 @@
       <c r="X10" s="5"/>
       <c r="Y10" s="5"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
@@ -827,7 +827,7 @@
       <c r="X11" s="5"/>
       <c r="Y11" s="5"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>25</v>
       </c>
@@ -864,7 +864,7 @@
       <c r="X12" s="5"/>
       <c r="Y12" s="5"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>27</v>
       </c>
@@ -901,7 +901,7 @@
       <c r="X13" s="5"/>
       <c r="Y13" s="5"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>29</v>
       </c>
@@ -938,7 +938,7 @@
       <c r="X14" s="5"/>
       <c r="Y14" s="5"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>31</v>
       </c>
@@ -975,7 +975,7 @@
       <c r="X15" s="5"/>
       <c r="Y15" s="5"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>33</v>
       </c>
@@ -1012,7 +1012,7 @@
       <c r="X16" s="5"/>
       <c r="Y16" s="5"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="6" t="s">
         <v>35</v>
       </c>
@@ -1049,7 +1049,7 @@
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1076,7 +1076,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1103,7 +1103,7 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1130,7 +1130,7 @@
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1157,7 +1157,7 @@
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1184,7 +1184,7 @@
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1211,7 +1211,7 @@
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1238,7 +1238,7 @@
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1265,7 +1265,7 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1292,7 +1292,7 @@
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1319,7 +1319,7 @@
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1346,7 +1346,7 @@
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1373,7 +1373,7 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1400,7 +1400,7 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1427,7 +1427,7 @@
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1454,7 +1454,7 @@
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1481,7 +1481,7 @@
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1508,7 +1508,7 @@
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1535,7 +1535,7 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1562,7 +1562,7 @@
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1589,7 +1589,7 @@
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1616,7 +1616,7 @@
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1643,7 +1643,7 @@
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1670,7 +1670,7 @@
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -1697,7 +1697,7 @@
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -1724,7 +1724,7 @@
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -1751,7 +1751,7 @@
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -1778,7 +1778,7 @@
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -1805,7 +1805,7 @@
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -1832,7 +1832,7 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1859,7 +1859,7 @@
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -1886,7 +1886,7 @@
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -1913,7 +1913,7 @@
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1940,7 +1940,7 @@
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -1967,7 +1967,7 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -1994,7 +1994,7 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2021,7 +2021,7 @@
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2048,7 +2048,7 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2075,7 +2075,7 @@
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2102,7 +2102,7 @@
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2129,7 +2129,7 @@
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2156,7 +2156,7 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2183,7 +2183,7 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2210,7 +2210,7 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2237,7 +2237,7 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2264,7 +2264,7 @@
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2291,7 +2291,7 @@
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2318,7 +2318,7 @@
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2345,7 +2345,7 @@
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2372,7 +2372,7 @@
       <c r="X66" s="1"/>
       <c r="Y66" s="1"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2399,7 +2399,7 @@
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2426,7 +2426,7 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2453,7 +2453,7 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2480,7 +2480,7 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2507,7 +2507,7 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2534,7 +2534,7 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2561,7 +2561,7 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2588,7 +2588,7 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2615,7 +2615,7 @@
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2642,7 +2642,7 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2669,7 +2669,7 @@
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -2696,7 +2696,7 @@
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -2723,7 +2723,7 @@
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -2750,7 +2750,7 @@
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -2777,7 +2777,7 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -2804,7 +2804,7 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -2831,7 +2831,7 @@
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -2858,7 +2858,7 @@
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -2885,7 +2885,7 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -2912,7 +2912,7 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -2939,7 +2939,7 @@
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -2966,7 +2966,7 @@
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -2993,7 +2993,7 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3020,7 +3020,7 @@
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3047,7 +3047,7 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3074,7 +3074,7 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3101,7 +3101,7 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3128,7 +3128,7 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3155,7 +3155,7 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3182,7 +3182,7 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3209,7 +3209,7 @@
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3236,7 +3236,7 @@
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3263,7 +3263,7 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3290,7 +3290,7 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3317,7 +3317,7 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3344,7 +3344,7 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3371,7 +3371,7 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3398,7 +3398,7 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3425,7 +3425,7 @@
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3452,7 +3452,7 @@
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3479,7 +3479,7 @@
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3506,7 +3506,7 @@
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3533,7 +3533,7 @@
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3560,7 +3560,7 @@
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3587,7 +3587,7 @@
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -3614,7 +3614,7 @@
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -3641,7 +3641,7 @@
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -3668,7 +3668,7 @@
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -3695,7 +3695,7 @@
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -3722,7 +3722,7 @@
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -3749,7 +3749,7 @@
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -3776,7 +3776,7 @@
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3803,7 +3803,7 @@
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -3830,7 +3830,7 @@
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -3857,7 +3857,7 @@
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -3884,7 +3884,7 @@
       <c r="X122" s="1"/>
       <c r="Y122" s="1"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -3911,7 +3911,7 @@
       <c r="X123" s="1"/>
       <c r="Y123" s="1"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -3938,7 +3938,7 @@
       <c r="X124" s="1"/>
       <c r="Y124" s="1"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -3965,7 +3965,7 @@
       <c r="X125" s="1"/>
       <c r="Y125" s="1"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -3992,7 +3992,7 @@
       <c r="X126" s="1"/>
       <c r="Y126" s="1"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4019,7 +4019,7 @@
       <c r="X127" s="1"/>
       <c r="Y127" s="1"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4046,7 +4046,7 @@
       <c r="X128" s="1"/>
       <c r="Y128" s="1"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4073,7 +4073,7 @@
       <c r="X129" s="1"/>
       <c r="Y129" s="1"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4100,7 +4100,7 @@
       <c r="X130" s="1"/>
       <c r="Y130" s="1"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4127,7 +4127,7 @@
       <c r="X131" s="1"/>
       <c r="Y131" s="1"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4154,7 +4154,7 @@
       <c r="X132" s="1"/>
       <c r="Y132" s="1"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4181,7 +4181,7 @@
       <c r="X133" s="1"/>
       <c r="Y133" s="1"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4208,7 +4208,7 @@
       <c r="X134" s="1"/>
       <c r="Y134" s="1"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4235,7 +4235,7 @@
       <c r="X135" s="1"/>
       <c r="Y135" s="1"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4262,7 +4262,7 @@
       <c r="X136" s="1"/>
       <c r="Y136" s="1"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4289,7 +4289,7 @@
       <c r="X137" s="1"/>
       <c r="Y137" s="1"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4316,7 +4316,7 @@
       <c r="X138" s="1"/>
       <c r="Y138" s="1"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4343,7 +4343,7 @@
       <c r="X139" s="1"/>
       <c r="Y139" s="1"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4370,7 +4370,7 @@
       <c r="X140" s="1"/>
       <c r="Y140" s="1"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4397,7 +4397,7 @@
       <c r="X141" s="1"/>
       <c r="Y141" s="1"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4424,7 +4424,7 @@
       <c r="X142" s="1"/>
       <c r="Y142" s="1"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -4451,7 +4451,7 @@
       <c r="X143" s="1"/>
       <c r="Y143" s="1"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -4478,7 +4478,7 @@
       <c r="X144" s="1"/>
       <c r="Y144" s="1"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -4505,7 +4505,7 @@
       <c r="X145" s="1"/>
       <c r="Y145" s="1"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -4532,7 +4532,7 @@
       <c r="X146" s="1"/>
       <c r="Y146" s="1"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -4559,7 +4559,7 @@
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -4586,7 +4586,7 @@
       <c r="X148" s="1"/>
       <c r="Y148" s="1"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -4613,7 +4613,7 @@
       <c r="X149" s="1"/>
       <c r="Y149" s="1"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -4640,7 +4640,7 @@
       <c r="X150" s="1"/>
       <c r="Y150" s="1"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -4667,7 +4667,7 @@
       <c r="X151" s="1"/>
       <c r="Y151" s="1"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4694,7 +4694,7 @@
       <c r="X152" s="1"/>
       <c r="Y152" s="1"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4721,7 +4721,7 @@
       <c r="X153" s="1"/>
       <c r="Y153" s="1"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4748,7 +4748,7 @@
       <c r="X154" s="1"/>
       <c r="Y154" s="1"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -4775,7 +4775,7 @@
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -4802,7 +4802,7 @@
       <c r="X156" s="1"/>
       <c r="Y156" s="1"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -4829,7 +4829,7 @@
       <c r="X157" s="1"/>
       <c r="Y157" s="1"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -4856,7 +4856,7 @@
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -4883,7 +4883,7 @@
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -4910,7 +4910,7 @@
       <c r="X160" s="1"/>
       <c r="Y160" s="1"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -4937,7 +4937,7 @@
       <c r="X161" s="1"/>
       <c r="Y161" s="1"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -4964,7 +4964,7 @@
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -4991,7 +4991,7 @@
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5018,7 +5018,7 @@
       <c r="X164" s="1"/>
       <c r="Y164" s="1"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5045,7 +5045,7 @@
       <c r="X165" s="1"/>
       <c r="Y165" s="1"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5072,7 +5072,7 @@
       <c r="X166" s="1"/>
       <c r="Y166" s="1"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5099,7 +5099,7 @@
       <c r="X167" s="1"/>
       <c r="Y167" s="1"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5126,7 +5126,7 @@
       <c r="X168" s="1"/>
       <c r="Y168" s="1"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5153,7 +5153,7 @@
       <c r="X169" s="1"/>
       <c r="Y169" s="1"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -5180,7 +5180,7 @@
       <c r="X170" s="1"/>
       <c r="Y170" s="1"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -5207,7 +5207,7 @@
       <c r="X171" s="1"/>
       <c r="Y171" s="1"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -5234,7 +5234,7 @@
       <c r="X172" s="1"/>
       <c r="Y172" s="1"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -5261,7 +5261,7 @@
       <c r="X173" s="1"/>
       <c r="Y173" s="1"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -5288,7 +5288,7 @@
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -5315,7 +5315,7 @@
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -5342,7 +5342,7 @@
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -5369,7 +5369,7 @@
       <c r="X177" s="1"/>
       <c r="Y177" s="1"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -5396,7 +5396,7 @@
       <c r="X178" s="1"/>
       <c r="Y178" s="1"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -5423,7 +5423,7 @@
       <c r="X179" s="1"/>
       <c r="Y179" s="1"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -5450,7 +5450,7 @@
       <c r="X180" s="1"/>
       <c r="Y180" s="1"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -5477,7 +5477,7 @@
       <c r="X181" s="1"/>
       <c r="Y181" s="1"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -5504,7 +5504,7 @@
       <c r="X182" s="1"/>
       <c r="Y182" s="1"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -5531,7 +5531,7 @@
       <c r="X183" s="1"/>
       <c r="Y183" s="1"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -5558,7 +5558,7 @@
       <c r="X184" s="1"/>
       <c r="Y184" s="1"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -5585,7 +5585,7 @@
       <c r="X185" s="1"/>
       <c r="Y185" s="1"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -5612,7 +5612,7 @@
       <c r="X186" s="1"/>
       <c r="Y186" s="1"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -5639,7 +5639,7 @@
       <c r="X187" s="1"/>
       <c r="Y187" s="1"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" ht="15.0" customHeight="1">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -5666,7 +5666,7 @@
       <c r="X188" s="1"/>
       <c r="Y188" s="1"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" ht="15.0" customHeight="1">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -5693,7 +5693,7 @@
       <c r="X189" s="1"/>
       <c r="Y189" s="1"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -5720,7 +5720,7 @@
       <c r="X190" s="1"/>
       <c r="Y190" s="1"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -5747,7 +5747,7 @@
       <c r="X191" s="1"/>
       <c r="Y191" s="1"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" ht="15.0" customHeight="1">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -5774,7 +5774,7 @@
       <c r="X192" s="1"/>
       <c r="Y192" s="1"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" ht="15.0" customHeight="1">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -5801,7 +5801,7 @@
       <c r="X193" s="1"/>
       <c r="Y193" s="1"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" ht="15.0" customHeight="1">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -5828,7 +5828,7 @@
       <c r="X194" s="1"/>
       <c r="Y194" s="1"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" ht="15.0" customHeight="1">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -5855,7 +5855,7 @@
       <c r="X195" s="1"/>
       <c r="Y195" s="1"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" ht="15.0" customHeight="1">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -5882,7 +5882,7 @@
       <c r="X196" s="1"/>
       <c r="Y196" s="1"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" ht="15.0" customHeight="1">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -5909,7 +5909,7 @@
       <c r="X197" s="1"/>
       <c r="Y197" s="1"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" ht="15.0" customHeight="1">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -5936,7 +5936,7 @@
       <c r="X198" s="1"/>
       <c r="Y198" s="1"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" ht="15.0" customHeight="1">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -5963,7 +5963,7 @@
       <c r="X199" s="1"/>
       <c r="Y199" s="1"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" ht="15.0" customHeight="1">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -5990,7 +5990,7 @@
       <c r="X200" s="1"/>
       <c r="Y200" s="1"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" ht="15.0" customHeight="1">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -6017,7 +6017,7 @@
       <c r="X201" s="1"/>
       <c r="Y201" s="1"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" ht="15.0" customHeight="1">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -6044,7 +6044,7 @@
       <c r="X202" s="1"/>
       <c r="Y202" s="1"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" ht="15.0" customHeight="1">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -6071,7 +6071,7 @@
       <c r="X203" s="1"/>
       <c r="Y203" s="1"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" ht="15.0" customHeight="1">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -6098,7 +6098,7 @@
       <c r="X204" s="1"/>
       <c r="Y204" s="1"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" ht="15.0" customHeight="1">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -6125,7 +6125,7 @@
       <c r="X205" s="1"/>
       <c r="Y205" s="1"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" ht="15.0" customHeight="1">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -6152,7 +6152,7 @@
       <c r="X206" s="1"/>
       <c r="Y206" s="1"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" ht="15.0" customHeight="1">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -6179,7 +6179,7 @@
       <c r="X207" s="1"/>
       <c r="Y207" s="1"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" ht="15.0" customHeight="1">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -6206,7 +6206,7 @@
       <c r="X208" s="1"/>
       <c r="Y208" s="1"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" ht="15.0" customHeight="1">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -6233,7 +6233,7 @@
       <c r="X209" s="1"/>
       <c r="Y209" s="1"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" ht="15.0" customHeight="1">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -6260,7 +6260,7 @@
       <c r="X210" s="1"/>
       <c r="Y210" s="1"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" ht="15.0" customHeight="1">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -6287,7 +6287,7 @@
       <c r="X211" s="1"/>
       <c r="Y211" s="1"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" ht="15.0" customHeight="1">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -6314,7 +6314,7 @@
       <c r="X212" s="1"/>
       <c r="Y212" s="1"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" ht="15.0" customHeight="1">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -6341,7 +6341,7 @@
       <c r="X213" s="1"/>
       <c r="Y213" s="1"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" ht="15.0" customHeight="1">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -6368,7 +6368,7 @@
       <c r="X214" s="1"/>
       <c r="Y214" s="1"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" ht="15.0" customHeight="1">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -6395,7 +6395,7 @@
       <c r="X215" s="1"/>
       <c r="Y215" s="1"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" ht="15.0" customHeight="1">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -6422,7 +6422,7 @@
       <c r="X216" s="1"/>
       <c r="Y216" s="1"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" ht="15.0" customHeight="1">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -6449,7 +6449,7 @@
       <c r="X217" s="1"/>
       <c r="Y217" s="1"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" ht="15.0" customHeight="1">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -6476,7 +6476,7 @@
       <c r="X218" s="1"/>
       <c r="Y218" s="1"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" ht="15.0" customHeight="1">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -6503,7 +6503,7 @@
       <c r="X219" s="1"/>
       <c r="Y219" s="1"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" ht="15.0" customHeight="1">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -6530,786 +6530,786 @@
       <c r="X220" s="1"/>
       <c r="Y220" s="1"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.0" customHeight="1"/>
+    <row r="222" ht="15.0" customHeight="1"/>
+    <row r="223" ht="15.0" customHeight="1"/>
+    <row r="224" ht="15.0" customHeight="1"/>
+    <row r="225" ht="15.0" customHeight="1"/>
+    <row r="226" ht="15.0" customHeight="1"/>
+    <row r="227" ht="15.0" customHeight="1"/>
+    <row r="228" ht="15.0" customHeight="1"/>
+    <row r="229" ht="15.0" customHeight="1"/>
+    <row r="230" ht="15.0" customHeight="1"/>
+    <row r="231" ht="15.0" customHeight="1"/>
+    <row r="232" ht="15.0" customHeight="1"/>
+    <row r="233" ht="15.0" customHeight="1"/>
+    <row r="234" ht="15.0" customHeight="1"/>
+    <row r="235" ht="15.0" customHeight="1"/>
+    <row r="236" ht="15.0" customHeight="1"/>
+    <row r="237" ht="15.0" customHeight="1"/>
+    <row r="238" ht="15.0" customHeight="1"/>
+    <row r="239" ht="15.0" customHeight="1"/>
+    <row r="240" ht="15.0" customHeight="1"/>
+    <row r="241" ht="15.0" customHeight="1"/>
+    <row r="242" ht="15.0" customHeight="1"/>
+    <row r="243" ht="15.0" customHeight="1"/>
+    <row r="244" ht="15.0" customHeight="1"/>
+    <row r="245" ht="15.0" customHeight="1"/>
+    <row r="246" ht="15.0" customHeight="1"/>
+    <row r="247" ht="15.0" customHeight="1"/>
+    <row r="248" ht="15.0" customHeight="1"/>
+    <row r="249" ht="15.0" customHeight="1"/>
+    <row r="250" ht="15.0" customHeight="1"/>
+    <row r="251" ht="15.0" customHeight="1"/>
+    <row r="252" ht="15.0" customHeight="1"/>
+    <row r="253" ht="15.0" customHeight="1"/>
+    <row r="254" ht="15.0" customHeight="1"/>
+    <row r="255" ht="15.0" customHeight="1"/>
+    <row r="256" ht="15.0" customHeight="1"/>
+    <row r="257" ht="15.0" customHeight="1"/>
+    <row r="258" ht="15.0" customHeight="1"/>
+    <row r="259" ht="15.0" customHeight="1"/>
+    <row r="260" ht="15.0" customHeight="1"/>
+    <row r="261" ht="15.0" customHeight="1"/>
+    <row r="262" ht="15.0" customHeight="1"/>
+    <row r="263" ht="15.0" customHeight="1"/>
+    <row r="264" ht="15.0" customHeight="1"/>
+    <row r="265" ht="15.0" customHeight="1"/>
+    <row r="266" ht="15.0" customHeight="1"/>
+    <row r="267" ht="15.0" customHeight="1"/>
+    <row r="268" ht="15.0" customHeight="1"/>
+    <row r="269" ht="15.0" customHeight="1"/>
+    <row r="270" ht="15.0" customHeight="1"/>
+    <row r="271" ht="15.0" customHeight="1"/>
+    <row r="272" ht="15.0" customHeight="1"/>
+    <row r="273" ht="15.0" customHeight="1"/>
+    <row r="274" ht="15.0" customHeight="1"/>
+    <row r="275" ht="15.0" customHeight="1"/>
+    <row r="276" ht="15.0" customHeight="1"/>
+    <row r="277" ht="15.0" customHeight="1"/>
+    <row r="278" ht="15.0" customHeight="1"/>
+    <row r="279" ht="15.0" customHeight="1"/>
+    <row r="280" ht="15.0" customHeight="1"/>
+    <row r="281" ht="15.0" customHeight="1"/>
+    <row r="282" ht="15.0" customHeight="1"/>
+    <row r="283" ht="15.0" customHeight="1"/>
+    <row r="284" ht="15.0" customHeight="1"/>
+    <row r="285" ht="15.0" customHeight="1"/>
+    <row r="286" ht="15.0" customHeight="1"/>
+    <row r="287" ht="15.0" customHeight="1"/>
+    <row r="288" ht="15.0" customHeight="1"/>
+    <row r="289" ht="15.0" customHeight="1"/>
+    <row r="290" ht="15.0" customHeight="1"/>
+    <row r="291" ht="15.0" customHeight="1"/>
+    <row r="292" ht="15.0" customHeight="1"/>
+    <row r="293" ht="15.0" customHeight="1"/>
+    <row r="294" ht="15.0" customHeight="1"/>
+    <row r="295" ht="15.0" customHeight="1"/>
+    <row r="296" ht="15.0" customHeight="1"/>
+    <row r="297" ht="15.0" customHeight="1"/>
+    <row r="298" ht="15.0" customHeight="1"/>
+    <row r="299" ht="15.0" customHeight="1"/>
+    <row r="300" ht="15.0" customHeight="1"/>
+    <row r="301" ht="15.0" customHeight="1"/>
+    <row r="302" ht="15.0" customHeight="1"/>
+    <row r="303" ht="15.0" customHeight="1"/>
+    <row r="304" ht="15.0" customHeight="1"/>
+    <row r="305" ht="15.0" customHeight="1"/>
+    <row r="306" ht="15.0" customHeight="1"/>
+    <row r="307" ht="15.0" customHeight="1"/>
+    <row r="308" ht="15.0" customHeight="1"/>
+    <row r="309" ht="15.0" customHeight="1"/>
+    <row r="310" ht="15.0" customHeight="1"/>
+    <row r="311" ht="15.0" customHeight="1"/>
+    <row r="312" ht="15.0" customHeight="1"/>
+    <row r="313" ht="15.0" customHeight="1"/>
+    <row r="314" ht="15.0" customHeight="1"/>
+    <row r="315" ht="15.0" customHeight="1"/>
+    <row r="316" ht="15.0" customHeight="1"/>
+    <row r="317" ht="15.0" customHeight="1"/>
+    <row r="318" ht="15.0" customHeight="1"/>
+    <row r="319" ht="15.0" customHeight="1"/>
+    <row r="320" ht="15.0" customHeight="1"/>
+    <row r="321" ht="15.0" customHeight="1"/>
+    <row r="322" ht="15.0" customHeight="1"/>
+    <row r="323" ht="15.0" customHeight="1"/>
+    <row r="324" ht="15.0" customHeight="1"/>
+    <row r="325" ht="15.0" customHeight="1"/>
+    <row r="326" ht="15.0" customHeight="1"/>
+    <row r="327" ht="15.0" customHeight="1"/>
+    <row r="328" ht="15.0" customHeight="1"/>
+    <row r="329" ht="15.0" customHeight="1"/>
+    <row r="330" ht="15.0" customHeight="1"/>
+    <row r="331" ht="15.0" customHeight="1"/>
+    <row r="332" ht="15.0" customHeight="1"/>
+    <row r="333" ht="15.0" customHeight="1"/>
+    <row r="334" ht="15.0" customHeight="1"/>
+    <row r="335" ht="15.0" customHeight="1"/>
+    <row r="336" ht="15.0" customHeight="1"/>
+    <row r="337" ht="15.0" customHeight="1"/>
+    <row r="338" ht="15.0" customHeight="1"/>
+    <row r="339" ht="15.0" customHeight="1"/>
+    <row r="340" ht="15.0" customHeight="1"/>
+    <row r="341" ht="15.0" customHeight="1"/>
+    <row r="342" ht="15.0" customHeight="1"/>
+    <row r="343" ht="15.0" customHeight="1"/>
+    <row r="344" ht="15.0" customHeight="1"/>
+    <row r="345" ht="15.0" customHeight="1"/>
+    <row r="346" ht="15.0" customHeight="1"/>
+    <row r="347" ht="15.0" customHeight="1"/>
+    <row r="348" ht="15.0" customHeight="1"/>
+    <row r="349" ht="15.0" customHeight="1"/>
+    <row r="350" ht="15.0" customHeight="1"/>
+    <row r="351" ht="15.0" customHeight="1"/>
+    <row r="352" ht="15.0" customHeight="1"/>
+    <row r="353" ht="15.0" customHeight="1"/>
+    <row r="354" ht="15.0" customHeight="1"/>
+    <row r="355" ht="15.0" customHeight="1"/>
+    <row r="356" ht="15.0" customHeight="1"/>
+    <row r="357" ht="15.0" customHeight="1"/>
+    <row r="358" ht="15.0" customHeight="1"/>
+    <row r="359" ht="15.0" customHeight="1"/>
+    <row r="360" ht="15.0" customHeight="1"/>
+    <row r="361" ht="15.0" customHeight="1"/>
+    <row r="362" ht="15.0" customHeight="1"/>
+    <row r="363" ht="15.0" customHeight="1"/>
+    <row r="364" ht="15.0" customHeight="1"/>
+    <row r="365" ht="15.0" customHeight="1"/>
+    <row r="366" ht="15.0" customHeight="1"/>
+    <row r="367" ht="15.0" customHeight="1"/>
+    <row r="368" ht="15.0" customHeight="1"/>
+    <row r="369" ht="15.0" customHeight="1"/>
+    <row r="370" ht="15.0" customHeight="1"/>
+    <row r="371" ht="15.0" customHeight="1"/>
+    <row r="372" ht="15.0" customHeight="1"/>
+    <row r="373" ht="15.0" customHeight="1"/>
+    <row r="374" ht="15.0" customHeight="1"/>
+    <row r="375" ht="15.0" customHeight="1"/>
+    <row r="376" ht="15.0" customHeight="1"/>
+    <row r="377" ht="15.0" customHeight="1"/>
+    <row r="378" ht="15.0" customHeight="1"/>
+    <row r="379" ht="15.0" customHeight="1"/>
+    <row r="380" ht="15.0" customHeight="1"/>
+    <row r="381" ht="15.0" customHeight="1"/>
+    <row r="382" ht="15.0" customHeight="1"/>
+    <row r="383" ht="15.0" customHeight="1"/>
+    <row r="384" ht="15.0" customHeight="1"/>
+    <row r="385" ht="15.0" customHeight="1"/>
+    <row r="386" ht="15.0" customHeight="1"/>
+    <row r="387" ht="15.0" customHeight="1"/>
+    <row r="388" ht="15.0" customHeight="1"/>
+    <row r="389" ht="15.0" customHeight="1"/>
+    <row r="390" ht="15.0" customHeight="1"/>
+    <row r="391" ht="15.0" customHeight="1"/>
+    <row r="392" ht="15.0" customHeight="1"/>
+    <row r="393" ht="15.0" customHeight="1"/>
+    <row r="394" ht="15.0" customHeight="1"/>
+    <row r="395" ht="15.0" customHeight="1"/>
+    <row r="396" ht="15.0" customHeight="1"/>
+    <row r="397" ht="15.0" customHeight="1"/>
+    <row r="398" ht="15.0" customHeight="1"/>
+    <row r="399" ht="15.0" customHeight="1"/>
+    <row r="400" ht="15.0" customHeight="1"/>
+    <row r="401" ht="15.0" customHeight="1"/>
+    <row r="402" ht="15.0" customHeight="1"/>
+    <row r="403" ht="15.0" customHeight="1"/>
+    <row r="404" ht="15.0" customHeight="1"/>
+    <row r="405" ht="15.0" customHeight="1"/>
+    <row r="406" ht="15.0" customHeight="1"/>
+    <row r="407" ht="15.0" customHeight="1"/>
+    <row r="408" ht="15.0" customHeight="1"/>
+    <row r="409" ht="15.0" customHeight="1"/>
+    <row r="410" ht="15.0" customHeight="1"/>
+    <row r="411" ht="15.0" customHeight="1"/>
+    <row r="412" ht="15.0" customHeight="1"/>
+    <row r="413" ht="15.0" customHeight="1"/>
+    <row r="414" ht="15.0" customHeight="1"/>
+    <row r="415" ht="15.0" customHeight="1"/>
+    <row r="416" ht="15.0" customHeight="1"/>
+    <row r="417" ht="15.0" customHeight="1"/>
+    <row r="418" ht="15.0" customHeight="1"/>
+    <row r="419" ht="15.0" customHeight="1"/>
+    <row r="420" ht="15.0" customHeight="1"/>
+    <row r="421" ht="15.0" customHeight="1"/>
+    <row r="422" ht="15.0" customHeight="1"/>
+    <row r="423" ht="15.0" customHeight="1"/>
+    <row r="424" ht="15.0" customHeight="1"/>
+    <row r="425" ht="15.0" customHeight="1"/>
+    <row r="426" ht="15.0" customHeight="1"/>
+    <row r="427" ht="15.0" customHeight="1"/>
+    <row r="428" ht="15.0" customHeight="1"/>
+    <row r="429" ht="15.0" customHeight="1"/>
+    <row r="430" ht="15.0" customHeight="1"/>
+    <row r="431" ht="15.0" customHeight="1"/>
+    <row r="432" ht="15.0" customHeight="1"/>
+    <row r="433" ht="15.0" customHeight="1"/>
+    <row r="434" ht="15.0" customHeight="1"/>
+    <row r="435" ht="15.0" customHeight="1"/>
+    <row r="436" ht="15.0" customHeight="1"/>
+    <row r="437" ht="15.0" customHeight="1"/>
+    <row r="438" ht="15.0" customHeight="1"/>
+    <row r="439" ht="15.0" customHeight="1"/>
+    <row r="440" ht="15.0" customHeight="1"/>
+    <row r="441" ht="15.0" customHeight="1"/>
+    <row r="442" ht="15.0" customHeight="1"/>
+    <row r="443" ht="15.0" customHeight="1"/>
+    <row r="444" ht="15.0" customHeight="1"/>
+    <row r="445" ht="15.0" customHeight="1"/>
+    <row r="446" ht="15.0" customHeight="1"/>
+    <row r="447" ht="15.0" customHeight="1"/>
+    <row r="448" ht="15.0" customHeight="1"/>
+    <row r="449" ht="15.0" customHeight="1"/>
+    <row r="450" ht="15.0" customHeight="1"/>
+    <row r="451" ht="15.0" customHeight="1"/>
+    <row r="452" ht="15.0" customHeight="1"/>
+    <row r="453" ht="15.0" customHeight="1"/>
+    <row r="454" ht="15.0" customHeight="1"/>
+    <row r="455" ht="15.0" customHeight="1"/>
+    <row r="456" ht="15.0" customHeight="1"/>
+    <row r="457" ht="15.0" customHeight="1"/>
+    <row r="458" ht="15.0" customHeight="1"/>
+    <row r="459" ht="15.0" customHeight="1"/>
+    <row r="460" ht="15.0" customHeight="1"/>
+    <row r="461" ht="15.0" customHeight="1"/>
+    <row r="462" ht="15.0" customHeight="1"/>
+    <row r="463" ht="15.0" customHeight="1"/>
+    <row r="464" ht="15.0" customHeight="1"/>
+    <row r="465" ht="15.0" customHeight="1"/>
+    <row r="466" ht="15.0" customHeight="1"/>
+    <row r="467" ht="15.0" customHeight="1"/>
+    <row r="468" ht="15.0" customHeight="1"/>
+    <row r="469" ht="15.0" customHeight="1"/>
+    <row r="470" ht="15.0" customHeight="1"/>
+    <row r="471" ht="15.0" customHeight="1"/>
+    <row r="472" ht="15.0" customHeight="1"/>
+    <row r="473" ht="15.0" customHeight="1"/>
+    <row r="474" ht="15.0" customHeight="1"/>
+    <row r="475" ht="15.0" customHeight="1"/>
+    <row r="476" ht="15.0" customHeight="1"/>
+    <row r="477" ht="15.0" customHeight="1"/>
+    <row r="478" ht="15.0" customHeight="1"/>
+    <row r="479" ht="15.0" customHeight="1"/>
+    <row r="480" ht="15.0" customHeight="1"/>
+    <row r="481" ht="15.0" customHeight="1"/>
+    <row r="482" ht="15.0" customHeight="1"/>
+    <row r="483" ht="15.0" customHeight="1"/>
+    <row r="484" ht="15.0" customHeight="1"/>
+    <row r="485" ht="15.0" customHeight="1"/>
+    <row r="486" ht="15.0" customHeight="1"/>
+    <row r="487" ht="15.0" customHeight="1"/>
+    <row r="488" ht="15.0" customHeight="1"/>
+    <row r="489" ht="15.0" customHeight="1"/>
+    <row r="490" ht="15.0" customHeight="1"/>
+    <row r="491" ht="15.0" customHeight="1"/>
+    <row r="492" ht="15.0" customHeight="1"/>
+    <row r="493" ht="15.0" customHeight="1"/>
+    <row r="494" ht="15.0" customHeight="1"/>
+    <row r="495" ht="15.0" customHeight="1"/>
+    <row r="496" ht="15.0" customHeight="1"/>
+    <row r="497" ht="15.0" customHeight="1"/>
+    <row r="498" ht="15.0" customHeight="1"/>
+    <row r="499" ht="15.0" customHeight="1"/>
+    <row r="500" ht="15.0" customHeight="1"/>
+    <row r="501" ht="15.0" customHeight="1"/>
+    <row r="502" ht="15.0" customHeight="1"/>
+    <row r="503" ht="15.0" customHeight="1"/>
+    <row r="504" ht="15.0" customHeight="1"/>
+    <row r="505" ht="15.0" customHeight="1"/>
+    <row r="506" ht="15.0" customHeight="1"/>
+    <row r="507" ht="15.0" customHeight="1"/>
+    <row r="508" ht="15.0" customHeight="1"/>
+    <row r="509" ht="15.0" customHeight="1"/>
+    <row r="510" ht="15.0" customHeight="1"/>
+    <row r="511" ht="15.0" customHeight="1"/>
+    <row r="512" ht="15.0" customHeight="1"/>
+    <row r="513" ht="15.0" customHeight="1"/>
+    <row r="514" ht="15.0" customHeight="1"/>
+    <row r="515" ht="15.0" customHeight="1"/>
+    <row r="516" ht="15.0" customHeight="1"/>
+    <row r="517" ht="15.0" customHeight="1"/>
+    <row r="518" ht="15.0" customHeight="1"/>
+    <row r="519" ht="15.0" customHeight="1"/>
+    <row r="520" ht="15.0" customHeight="1"/>
+    <row r="521" ht="15.0" customHeight="1"/>
+    <row r="522" ht="15.0" customHeight="1"/>
+    <row r="523" ht="15.0" customHeight="1"/>
+    <row r="524" ht="15.0" customHeight="1"/>
+    <row r="525" ht="15.0" customHeight="1"/>
+    <row r="526" ht="15.0" customHeight="1"/>
+    <row r="527" ht="15.0" customHeight="1"/>
+    <row r="528" ht="15.0" customHeight="1"/>
+    <row r="529" ht="15.0" customHeight="1"/>
+    <row r="530" ht="15.0" customHeight="1"/>
+    <row r="531" ht="15.0" customHeight="1"/>
+    <row r="532" ht="15.0" customHeight="1"/>
+    <row r="533" ht="15.0" customHeight="1"/>
+    <row r="534" ht="15.0" customHeight="1"/>
+    <row r="535" ht="15.0" customHeight="1"/>
+    <row r="536" ht="15.0" customHeight="1"/>
+    <row r="537" ht="15.0" customHeight="1"/>
+    <row r="538" ht="15.0" customHeight="1"/>
+    <row r="539" ht="15.0" customHeight="1"/>
+    <row r="540" ht="15.0" customHeight="1"/>
+    <row r="541" ht="15.0" customHeight="1"/>
+    <row r="542" ht="15.0" customHeight="1"/>
+    <row r="543" ht="15.0" customHeight="1"/>
+    <row r="544" ht="15.0" customHeight="1"/>
+    <row r="545" ht="15.0" customHeight="1"/>
+    <row r="546" ht="15.0" customHeight="1"/>
+    <row r="547" ht="15.0" customHeight="1"/>
+    <row r="548" ht="15.0" customHeight="1"/>
+    <row r="549" ht="15.0" customHeight="1"/>
+    <row r="550" ht="15.0" customHeight="1"/>
+    <row r="551" ht="15.0" customHeight="1"/>
+    <row r="552" ht="15.0" customHeight="1"/>
+    <row r="553" ht="15.0" customHeight="1"/>
+    <row r="554" ht="15.0" customHeight="1"/>
+    <row r="555" ht="15.0" customHeight="1"/>
+    <row r="556" ht="15.0" customHeight="1"/>
+    <row r="557" ht="15.0" customHeight="1"/>
+    <row r="558" ht="15.0" customHeight="1"/>
+    <row r="559" ht="15.0" customHeight="1"/>
+    <row r="560" ht="15.0" customHeight="1"/>
+    <row r="561" ht="15.0" customHeight="1"/>
+    <row r="562" ht="15.0" customHeight="1"/>
+    <row r="563" ht="15.0" customHeight="1"/>
+    <row r="564" ht="15.0" customHeight="1"/>
+    <row r="565" ht="15.0" customHeight="1"/>
+    <row r="566" ht="15.0" customHeight="1"/>
+    <row r="567" ht="15.0" customHeight="1"/>
+    <row r="568" ht="15.0" customHeight="1"/>
+    <row r="569" ht="15.0" customHeight="1"/>
+    <row r="570" ht="15.0" customHeight="1"/>
+    <row r="571" ht="15.0" customHeight="1"/>
+    <row r="572" ht="15.0" customHeight="1"/>
+    <row r="573" ht="15.0" customHeight="1"/>
+    <row r="574" ht="15.0" customHeight="1"/>
+    <row r="575" ht="15.0" customHeight="1"/>
+    <row r="576" ht="15.0" customHeight="1"/>
+    <row r="577" ht="15.0" customHeight="1"/>
+    <row r="578" ht="15.0" customHeight="1"/>
+    <row r="579" ht="15.0" customHeight="1"/>
+    <row r="580" ht="15.0" customHeight="1"/>
+    <row r="581" ht="15.0" customHeight="1"/>
+    <row r="582" ht="15.0" customHeight="1"/>
+    <row r="583" ht="15.0" customHeight="1"/>
+    <row r="584" ht="15.0" customHeight="1"/>
+    <row r="585" ht="15.0" customHeight="1"/>
+    <row r="586" ht="15.0" customHeight="1"/>
+    <row r="587" ht="15.0" customHeight="1"/>
+    <row r="588" ht="15.0" customHeight="1"/>
+    <row r="589" ht="15.0" customHeight="1"/>
+    <row r="590" ht="15.0" customHeight="1"/>
+    <row r="591" ht="15.0" customHeight="1"/>
+    <row r="592" ht="15.0" customHeight="1"/>
+    <row r="593" ht="15.0" customHeight="1"/>
+    <row r="594" ht="15.0" customHeight="1"/>
+    <row r="595" ht="15.0" customHeight="1"/>
+    <row r="596" ht="15.0" customHeight="1"/>
+    <row r="597" ht="15.0" customHeight="1"/>
+    <row r="598" ht="15.0" customHeight="1"/>
+    <row r="599" ht="15.0" customHeight="1"/>
+    <row r="600" ht="15.0" customHeight="1"/>
+    <row r="601" ht="15.0" customHeight="1"/>
+    <row r="602" ht="15.0" customHeight="1"/>
+    <row r="603" ht="15.0" customHeight="1"/>
+    <row r="604" ht="15.0" customHeight="1"/>
+    <row r="605" ht="15.0" customHeight="1"/>
+    <row r="606" ht="15.0" customHeight="1"/>
+    <row r="607" ht="15.0" customHeight="1"/>
+    <row r="608" ht="15.0" customHeight="1"/>
+    <row r="609" ht="15.0" customHeight="1"/>
+    <row r="610" ht="15.0" customHeight="1"/>
+    <row r="611" ht="15.0" customHeight="1"/>
+    <row r="612" ht="15.0" customHeight="1"/>
+    <row r="613" ht="15.0" customHeight="1"/>
+    <row r="614" ht="15.0" customHeight="1"/>
+    <row r="615" ht="15.0" customHeight="1"/>
+    <row r="616" ht="15.0" customHeight="1"/>
+    <row r="617" ht="15.0" customHeight="1"/>
+    <row r="618" ht="15.0" customHeight="1"/>
+    <row r="619" ht="15.0" customHeight="1"/>
+    <row r="620" ht="15.0" customHeight="1"/>
+    <row r="621" ht="15.0" customHeight="1"/>
+    <row r="622" ht="15.0" customHeight="1"/>
+    <row r="623" ht="15.0" customHeight="1"/>
+    <row r="624" ht="15.0" customHeight="1"/>
+    <row r="625" ht="15.0" customHeight="1"/>
+    <row r="626" ht="15.0" customHeight="1"/>
+    <row r="627" ht="15.0" customHeight="1"/>
+    <row r="628" ht="15.0" customHeight="1"/>
+    <row r="629" ht="15.0" customHeight="1"/>
+    <row r="630" ht="15.0" customHeight="1"/>
+    <row r="631" ht="15.0" customHeight="1"/>
+    <row r="632" ht="15.0" customHeight="1"/>
+    <row r="633" ht="15.0" customHeight="1"/>
+    <row r="634" ht="15.0" customHeight="1"/>
+    <row r="635" ht="15.0" customHeight="1"/>
+    <row r="636" ht="15.0" customHeight="1"/>
+    <row r="637" ht="15.0" customHeight="1"/>
+    <row r="638" ht="15.0" customHeight="1"/>
+    <row r="639" ht="15.0" customHeight="1"/>
+    <row r="640" ht="15.0" customHeight="1"/>
+    <row r="641" ht="15.0" customHeight="1"/>
+    <row r="642" ht="15.0" customHeight="1"/>
+    <row r="643" ht="15.0" customHeight="1"/>
+    <row r="644" ht="15.0" customHeight="1"/>
+    <row r="645" ht="15.0" customHeight="1"/>
+    <row r="646" ht="15.0" customHeight="1"/>
+    <row r="647" ht="15.0" customHeight="1"/>
+    <row r="648" ht="15.0" customHeight="1"/>
+    <row r="649" ht="15.0" customHeight="1"/>
+    <row r="650" ht="15.0" customHeight="1"/>
+    <row r="651" ht="15.0" customHeight="1"/>
+    <row r="652" ht="15.0" customHeight="1"/>
+    <row r="653" ht="15.0" customHeight="1"/>
+    <row r="654" ht="15.0" customHeight="1"/>
+    <row r="655" ht="15.0" customHeight="1"/>
+    <row r="656" ht="15.0" customHeight="1"/>
+    <row r="657" ht="15.0" customHeight="1"/>
+    <row r="658" ht="15.0" customHeight="1"/>
+    <row r="659" ht="15.0" customHeight="1"/>
+    <row r="660" ht="15.0" customHeight="1"/>
+    <row r="661" ht="15.0" customHeight="1"/>
+    <row r="662" ht="15.0" customHeight="1"/>
+    <row r="663" ht="15.0" customHeight="1"/>
+    <row r="664" ht="15.0" customHeight="1"/>
+    <row r="665" ht="15.0" customHeight="1"/>
+    <row r="666" ht="15.0" customHeight="1"/>
+    <row r="667" ht="15.0" customHeight="1"/>
+    <row r="668" ht="15.0" customHeight="1"/>
+    <row r="669" ht="15.0" customHeight="1"/>
+    <row r="670" ht="15.0" customHeight="1"/>
+    <row r="671" ht="15.0" customHeight="1"/>
+    <row r="672" ht="15.0" customHeight="1"/>
+    <row r="673" ht="15.0" customHeight="1"/>
+    <row r="674" ht="15.0" customHeight="1"/>
+    <row r="675" ht="15.0" customHeight="1"/>
+    <row r="676" ht="15.0" customHeight="1"/>
+    <row r="677" ht="15.0" customHeight="1"/>
+    <row r="678" ht="15.0" customHeight="1"/>
+    <row r="679" ht="15.0" customHeight="1"/>
+    <row r="680" ht="15.0" customHeight="1"/>
+    <row r="681" ht="15.0" customHeight="1"/>
+    <row r="682" ht="15.0" customHeight="1"/>
+    <row r="683" ht="15.0" customHeight="1"/>
+    <row r="684" ht="15.0" customHeight="1"/>
+    <row r="685" ht="15.0" customHeight="1"/>
+    <row r="686" ht="15.0" customHeight="1"/>
+    <row r="687" ht="15.0" customHeight="1"/>
+    <row r="688" ht="15.0" customHeight="1"/>
+    <row r="689" ht="15.0" customHeight="1"/>
+    <row r="690" ht="15.0" customHeight="1"/>
+    <row r="691" ht="15.0" customHeight="1"/>
+    <row r="692" ht="15.0" customHeight="1"/>
+    <row r="693" ht="15.0" customHeight="1"/>
+    <row r="694" ht="15.0" customHeight="1"/>
+    <row r="695" ht="15.0" customHeight="1"/>
+    <row r="696" ht="15.0" customHeight="1"/>
+    <row r="697" ht="15.0" customHeight="1"/>
+    <row r="698" ht="15.0" customHeight="1"/>
+    <row r="699" ht="15.0" customHeight="1"/>
+    <row r="700" ht="15.0" customHeight="1"/>
+    <row r="701" ht="15.0" customHeight="1"/>
+    <row r="702" ht="15.0" customHeight="1"/>
+    <row r="703" ht="15.0" customHeight="1"/>
+    <row r="704" ht="15.0" customHeight="1"/>
+    <row r="705" ht="15.0" customHeight="1"/>
+    <row r="706" ht="15.0" customHeight="1"/>
+    <row r="707" ht="15.0" customHeight="1"/>
+    <row r="708" ht="15.0" customHeight="1"/>
+    <row r="709" ht="15.0" customHeight="1"/>
+    <row r="710" ht="15.0" customHeight="1"/>
+    <row r="711" ht="15.0" customHeight="1"/>
+    <row r="712" ht="15.0" customHeight="1"/>
+    <row r="713" ht="15.0" customHeight="1"/>
+    <row r="714" ht="15.0" customHeight="1"/>
+    <row r="715" ht="15.0" customHeight="1"/>
+    <row r="716" ht="15.0" customHeight="1"/>
+    <row r="717" ht="15.0" customHeight="1"/>
+    <row r="718" ht="15.0" customHeight="1"/>
+    <row r="719" ht="15.0" customHeight="1"/>
+    <row r="720" ht="15.0" customHeight="1"/>
+    <row r="721" ht="15.0" customHeight="1"/>
+    <row r="722" ht="15.0" customHeight="1"/>
+    <row r="723" ht="15.0" customHeight="1"/>
+    <row r="724" ht="15.0" customHeight="1"/>
+    <row r="725" ht="15.0" customHeight="1"/>
+    <row r="726" ht="15.0" customHeight="1"/>
+    <row r="727" ht="15.0" customHeight="1"/>
+    <row r="728" ht="15.0" customHeight="1"/>
+    <row r="729" ht="15.0" customHeight="1"/>
+    <row r="730" ht="15.0" customHeight="1"/>
+    <row r="731" ht="15.0" customHeight="1"/>
+    <row r="732" ht="15.0" customHeight="1"/>
+    <row r="733" ht="15.0" customHeight="1"/>
+    <row r="734" ht="15.0" customHeight="1"/>
+    <row r="735" ht="15.0" customHeight="1"/>
+    <row r="736" ht="15.0" customHeight="1"/>
+    <row r="737" ht="15.0" customHeight="1"/>
+    <row r="738" ht="15.0" customHeight="1"/>
+    <row r="739" ht="15.0" customHeight="1"/>
+    <row r="740" ht="15.0" customHeight="1"/>
+    <row r="741" ht="15.0" customHeight="1"/>
+    <row r="742" ht="15.0" customHeight="1"/>
+    <row r="743" ht="15.0" customHeight="1"/>
+    <row r="744" ht="15.0" customHeight="1"/>
+    <row r="745" ht="15.0" customHeight="1"/>
+    <row r="746" ht="15.0" customHeight="1"/>
+    <row r="747" ht="15.0" customHeight="1"/>
+    <row r="748" ht="15.0" customHeight="1"/>
+    <row r="749" ht="15.0" customHeight="1"/>
+    <row r="750" ht="15.0" customHeight="1"/>
+    <row r="751" ht="15.0" customHeight="1"/>
+    <row r="752" ht="15.0" customHeight="1"/>
+    <row r="753" ht="15.0" customHeight="1"/>
+    <row r="754" ht="15.0" customHeight="1"/>
+    <row r="755" ht="15.0" customHeight="1"/>
+    <row r="756" ht="15.0" customHeight="1"/>
+    <row r="757" ht="15.0" customHeight="1"/>
+    <row r="758" ht="15.0" customHeight="1"/>
+    <row r="759" ht="15.0" customHeight="1"/>
+    <row r="760" ht="15.0" customHeight="1"/>
+    <row r="761" ht="15.0" customHeight="1"/>
+    <row r="762" ht="15.0" customHeight="1"/>
+    <row r="763" ht="15.0" customHeight="1"/>
+    <row r="764" ht="15.0" customHeight="1"/>
+    <row r="765" ht="15.0" customHeight="1"/>
+    <row r="766" ht="15.0" customHeight="1"/>
+    <row r="767" ht="15.0" customHeight="1"/>
+    <row r="768" ht="15.0" customHeight="1"/>
+    <row r="769" ht="15.0" customHeight="1"/>
+    <row r="770" ht="15.0" customHeight="1"/>
+    <row r="771" ht="15.0" customHeight="1"/>
+    <row r="772" ht="15.0" customHeight="1"/>
+    <row r="773" ht="15.0" customHeight="1"/>
+    <row r="774" ht="15.0" customHeight="1"/>
+    <row r="775" ht="15.0" customHeight="1"/>
+    <row r="776" ht="15.0" customHeight="1"/>
+    <row r="777" ht="15.0" customHeight="1"/>
+    <row r="778" ht="15.0" customHeight="1"/>
+    <row r="779" ht="15.0" customHeight="1"/>
+    <row r="780" ht="15.0" customHeight="1"/>
+    <row r="781" ht="15.0" customHeight="1"/>
+    <row r="782" ht="15.0" customHeight="1"/>
+    <row r="783" ht="15.0" customHeight="1"/>
+    <row r="784" ht="15.0" customHeight="1"/>
+    <row r="785" ht="15.0" customHeight="1"/>
+    <row r="786" ht="15.0" customHeight="1"/>
+    <row r="787" ht="15.0" customHeight="1"/>
+    <row r="788" ht="15.0" customHeight="1"/>
+    <row r="789" ht="15.0" customHeight="1"/>
+    <row r="790" ht="15.0" customHeight="1"/>
+    <row r="791" ht="15.0" customHeight="1"/>
+    <row r="792" ht="15.0" customHeight="1"/>
+    <row r="793" ht="15.0" customHeight="1"/>
+    <row r="794" ht="15.0" customHeight="1"/>
+    <row r="795" ht="15.0" customHeight="1"/>
+    <row r="796" ht="15.0" customHeight="1"/>
+    <row r="797" ht="15.0" customHeight="1"/>
+    <row r="798" ht="15.0" customHeight="1"/>
+    <row r="799" ht="15.0" customHeight="1"/>
+    <row r="800" ht="15.0" customHeight="1"/>
+    <row r="801" ht="15.0" customHeight="1"/>
+    <row r="802" ht="15.0" customHeight="1"/>
+    <row r="803" ht="15.0" customHeight="1"/>
+    <row r="804" ht="15.0" customHeight="1"/>
+    <row r="805" ht="15.0" customHeight="1"/>
+    <row r="806" ht="15.0" customHeight="1"/>
+    <row r="807" ht="15.0" customHeight="1"/>
+    <row r="808" ht="15.0" customHeight="1"/>
+    <row r="809" ht="15.0" customHeight="1"/>
+    <row r="810" ht="15.0" customHeight="1"/>
+    <row r="811" ht="15.0" customHeight="1"/>
+    <row r="812" ht="15.0" customHeight="1"/>
+    <row r="813" ht="15.0" customHeight="1"/>
+    <row r="814" ht="15.0" customHeight="1"/>
+    <row r="815" ht="15.0" customHeight="1"/>
+    <row r="816" ht="15.0" customHeight="1"/>
+    <row r="817" ht="15.0" customHeight="1"/>
+    <row r="818" ht="15.0" customHeight="1"/>
+    <row r="819" ht="15.0" customHeight="1"/>
+    <row r="820" ht="15.0" customHeight="1"/>
+    <row r="821" ht="15.0" customHeight="1"/>
+    <row r="822" ht="15.0" customHeight="1"/>
+    <row r="823" ht="15.0" customHeight="1"/>
+    <row r="824" ht="15.0" customHeight="1"/>
+    <row r="825" ht="15.0" customHeight="1"/>
+    <row r="826" ht="15.0" customHeight="1"/>
+    <row r="827" ht="15.0" customHeight="1"/>
+    <row r="828" ht="15.0" customHeight="1"/>
+    <row r="829" ht="15.0" customHeight="1"/>
+    <row r="830" ht="15.0" customHeight="1"/>
+    <row r="831" ht="15.0" customHeight="1"/>
+    <row r="832" ht="15.0" customHeight="1"/>
+    <row r="833" ht="15.0" customHeight="1"/>
+    <row r="834" ht="15.0" customHeight="1"/>
+    <row r="835" ht="15.0" customHeight="1"/>
+    <row r="836" ht="15.0" customHeight="1"/>
+    <row r="837" ht="15.0" customHeight="1"/>
+    <row r="838" ht="15.0" customHeight="1"/>
+    <row r="839" ht="15.0" customHeight="1"/>
+    <row r="840" ht="15.0" customHeight="1"/>
+    <row r="841" ht="15.0" customHeight="1"/>
+    <row r="842" ht="15.0" customHeight="1"/>
+    <row r="843" ht="15.0" customHeight="1"/>
+    <row r="844" ht="15.0" customHeight="1"/>
+    <row r="845" ht="15.0" customHeight="1"/>
+    <row r="846" ht="15.0" customHeight="1"/>
+    <row r="847" ht="15.0" customHeight="1"/>
+    <row r="848" ht="15.0" customHeight="1"/>
+    <row r="849" ht="15.0" customHeight="1"/>
+    <row r="850" ht="15.0" customHeight="1"/>
+    <row r="851" ht="15.0" customHeight="1"/>
+    <row r="852" ht="15.0" customHeight="1"/>
+    <row r="853" ht="15.0" customHeight="1"/>
+    <row r="854" ht="15.0" customHeight="1"/>
+    <row r="855" ht="15.0" customHeight="1"/>
+    <row r="856" ht="15.0" customHeight="1"/>
+    <row r="857" ht="15.0" customHeight="1"/>
+    <row r="858" ht="15.0" customHeight="1"/>
+    <row r="859" ht="15.0" customHeight="1"/>
+    <row r="860" ht="15.0" customHeight="1"/>
+    <row r="861" ht="15.0" customHeight="1"/>
+    <row r="862" ht="15.0" customHeight="1"/>
+    <row r="863" ht="15.0" customHeight="1"/>
+    <row r="864" ht="15.0" customHeight="1"/>
+    <row r="865" ht="15.0" customHeight="1"/>
+    <row r="866" ht="15.0" customHeight="1"/>
+    <row r="867" ht="15.0" customHeight="1"/>
+    <row r="868" ht="15.0" customHeight="1"/>
+    <row r="869" ht="15.0" customHeight="1"/>
+    <row r="870" ht="15.0" customHeight="1"/>
+    <row r="871" ht="15.0" customHeight="1"/>
+    <row r="872" ht="15.0" customHeight="1"/>
+    <row r="873" ht="15.0" customHeight="1"/>
+    <row r="874" ht="15.0" customHeight="1"/>
+    <row r="875" ht="15.0" customHeight="1"/>
+    <row r="876" ht="15.0" customHeight="1"/>
+    <row r="877" ht="15.0" customHeight="1"/>
+    <row r="878" ht="15.0" customHeight="1"/>
+    <row r="879" ht="15.0" customHeight="1"/>
+    <row r="880" ht="15.0" customHeight="1"/>
+    <row r="881" ht="15.0" customHeight="1"/>
+    <row r="882" ht="15.0" customHeight="1"/>
+    <row r="883" ht="15.0" customHeight="1"/>
+    <row r="884" ht="15.0" customHeight="1"/>
+    <row r="885" ht="15.0" customHeight="1"/>
+    <row r="886" ht="15.0" customHeight="1"/>
+    <row r="887" ht="15.0" customHeight="1"/>
+    <row r="888" ht="15.0" customHeight="1"/>
+    <row r="889" ht="15.0" customHeight="1"/>
+    <row r="890" ht="15.0" customHeight="1"/>
+    <row r="891" ht="15.0" customHeight="1"/>
+    <row r="892" ht="15.0" customHeight="1"/>
+    <row r="893" ht="15.0" customHeight="1"/>
+    <row r="894" ht="15.0" customHeight="1"/>
+    <row r="895" ht="15.0" customHeight="1"/>
+    <row r="896" ht="15.0" customHeight="1"/>
+    <row r="897" ht="15.0" customHeight="1"/>
+    <row r="898" ht="15.0" customHeight="1"/>
+    <row r="899" ht="15.0" customHeight="1"/>
+    <row r="900" ht="15.0" customHeight="1"/>
+    <row r="901" ht="15.0" customHeight="1"/>
+    <row r="902" ht="15.0" customHeight="1"/>
+    <row r="903" ht="15.0" customHeight="1"/>
+    <row r="904" ht="15.0" customHeight="1"/>
+    <row r="905" ht="15.0" customHeight="1"/>
+    <row r="906" ht="15.0" customHeight="1"/>
+    <row r="907" ht="15.0" customHeight="1"/>
+    <row r="908" ht="15.0" customHeight="1"/>
+    <row r="909" ht="15.0" customHeight="1"/>
+    <row r="910" ht="15.0" customHeight="1"/>
+    <row r="911" ht="15.0" customHeight="1"/>
+    <row r="912" ht="15.0" customHeight="1"/>
+    <row r="913" ht="15.0" customHeight="1"/>
+    <row r="914" ht="15.0" customHeight="1"/>
+    <row r="915" ht="15.0" customHeight="1"/>
+    <row r="916" ht="15.0" customHeight="1"/>
+    <row r="917" ht="15.0" customHeight="1"/>
+    <row r="918" ht="15.0" customHeight="1"/>
+    <row r="919" ht="15.0" customHeight="1"/>
+    <row r="920" ht="15.0" customHeight="1"/>
+    <row r="921" ht="15.0" customHeight="1"/>
+    <row r="922" ht="15.0" customHeight="1"/>
+    <row r="923" ht="15.0" customHeight="1"/>
+    <row r="924" ht="15.0" customHeight="1"/>
+    <row r="925" ht="15.0" customHeight="1"/>
+    <row r="926" ht="15.0" customHeight="1"/>
+    <row r="927" ht="15.0" customHeight="1"/>
+    <row r="928" ht="15.0" customHeight="1"/>
+    <row r="929" ht="15.0" customHeight="1"/>
+    <row r="930" ht="15.0" customHeight="1"/>
+    <row r="931" ht="15.0" customHeight="1"/>
+    <row r="932" ht="15.0" customHeight="1"/>
+    <row r="933" ht="15.0" customHeight="1"/>
+    <row r="934" ht="15.0" customHeight="1"/>
+    <row r="935" ht="15.0" customHeight="1"/>
+    <row r="936" ht="15.0" customHeight="1"/>
+    <row r="937" ht="15.0" customHeight="1"/>
+    <row r="938" ht="15.0" customHeight="1"/>
+    <row r="939" ht="15.0" customHeight="1"/>
+    <row r="940" ht="15.0" customHeight="1"/>
+    <row r="941" ht="15.0" customHeight="1"/>
+    <row r="942" ht="15.0" customHeight="1"/>
+    <row r="943" ht="15.0" customHeight="1"/>
+    <row r="944" ht="15.0" customHeight="1"/>
+    <row r="945" ht="15.0" customHeight="1"/>
+    <row r="946" ht="15.0" customHeight="1"/>
+    <row r="947" ht="15.0" customHeight="1"/>
+    <row r="948" ht="15.0" customHeight="1"/>
+    <row r="949" ht="15.0" customHeight="1"/>
+    <row r="950" ht="15.0" customHeight="1"/>
+    <row r="951" ht="15.0" customHeight="1"/>
+    <row r="952" ht="15.0" customHeight="1"/>
+    <row r="953" ht="15.0" customHeight="1"/>
+    <row r="954" ht="15.0" customHeight="1"/>
+    <row r="955" ht="15.0" customHeight="1"/>
+    <row r="956" ht="15.0" customHeight="1"/>
+    <row r="957" ht="15.0" customHeight="1"/>
+    <row r="958" ht="15.0" customHeight="1"/>
+    <row r="959" ht="15.0" customHeight="1"/>
+    <row r="960" ht="15.0" customHeight="1"/>
+    <row r="961" ht="15.0" customHeight="1"/>
+    <row r="962" ht="15.0" customHeight="1"/>
+    <row r="963" ht="15.0" customHeight="1"/>
+    <row r="964" ht="15.0" customHeight="1"/>
+    <row r="965" ht="15.0" customHeight="1"/>
+    <row r="966" ht="15.0" customHeight="1"/>
+    <row r="967" ht="15.0" customHeight="1"/>
+    <row r="968" ht="15.0" customHeight="1"/>
+    <row r="969" ht="15.0" customHeight="1"/>
+    <row r="970" ht="15.0" customHeight="1"/>
+    <row r="971" ht="15.0" customHeight="1"/>
+    <row r="972" ht="15.0" customHeight="1"/>
+    <row r="973" ht="15.0" customHeight="1"/>
+    <row r="974" ht="15.0" customHeight="1"/>
+    <row r="975" ht="15.0" customHeight="1"/>
+    <row r="976" ht="15.0" customHeight="1"/>
+    <row r="977" ht="15.0" customHeight="1"/>
+    <row r="978" ht="15.0" customHeight="1"/>
+    <row r="979" ht="15.0" customHeight="1"/>
+    <row r="980" ht="15.0" customHeight="1"/>
+    <row r="981" ht="15.0" customHeight="1"/>
+    <row r="982" ht="15.0" customHeight="1"/>
+    <row r="983" ht="15.0" customHeight="1"/>
+    <row r="984" ht="15.0" customHeight="1"/>
+    <row r="985" ht="15.0" customHeight="1"/>
+    <row r="986" ht="15.0" customHeight="1"/>
+    <row r="987" ht="15.0" customHeight="1"/>
+    <row r="988" ht="15.0" customHeight="1"/>
+    <row r="989" ht="15.0" customHeight="1"/>
+    <row r="990" ht="15.0" customHeight="1"/>
+    <row r="991" ht="15.0" customHeight="1"/>
+    <row r="992" ht="15.0" customHeight="1"/>
+    <row r="993" ht="15.0" customHeight="1"/>
+    <row r="994" ht="15.0" customHeight="1"/>
+    <row r="995" ht="15.0" customHeight="1"/>
+    <row r="996" ht="15.0" customHeight="1"/>
+    <row r="997" ht="15.0" customHeight="1"/>
+    <row r="998" ht="15.0" customHeight="1"/>
+    <row r="999" ht="15.0" customHeight="1"/>
+    <row r="1000" ht="15.0" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/ValueInfo/T_ValTable.xlsx
+++ b/Templates/Tables/ValueInfo/T_ValTable.xlsx
@@ -256,14 +256,14 @@
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="calibri"/>
+        <a:ea typeface="calibri"/>
+        <a:cs typeface="calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="calibri"/>
+        <a:ea typeface="calibri"/>
+        <a:cs typeface="calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -6530,786 +6530,786 @@
       <c r="X220" s="1"/>
       <c r="Y220" s="1"/>
     </row>
-    <row r="221" ht="15.0" customHeight="1"/>
-    <row r="222" ht="15.0" customHeight="1"/>
-    <row r="223" ht="15.0" customHeight="1"/>
-    <row r="224" ht="15.0" customHeight="1"/>
-    <row r="225" ht="15.0" customHeight="1"/>
-    <row r="226" ht="15.0" customHeight="1"/>
-    <row r="227" ht="15.0" customHeight="1"/>
-    <row r="228" ht="15.0" customHeight="1"/>
-    <row r="229" ht="15.0" customHeight="1"/>
-    <row r="230" ht="15.0" customHeight="1"/>
-    <row r="231" ht="15.0" customHeight="1"/>
-    <row r="232" ht="15.0" customHeight="1"/>
-    <row r="233" ht="15.0" customHeight="1"/>
-    <row r="234" ht="15.0" customHeight="1"/>
-    <row r="235" ht="15.0" customHeight="1"/>
-    <row r="236" ht="15.0" customHeight="1"/>
-    <row r="237" ht="15.0" customHeight="1"/>
-    <row r="238" ht="15.0" customHeight="1"/>
-    <row r="239" ht="15.0" customHeight="1"/>
-    <row r="240" ht="15.0" customHeight="1"/>
-    <row r="241" ht="15.0" customHeight="1"/>
-    <row r="242" ht="15.0" customHeight="1"/>
-    <row r="243" ht="15.0" customHeight="1"/>
-    <row r="244" ht="15.0" customHeight="1"/>
-    <row r="245" ht="15.0" customHeight="1"/>
-    <row r="246" ht="15.0" customHeight="1"/>
-    <row r="247" ht="15.0" customHeight="1"/>
-    <row r="248" ht="15.0" customHeight="1"/>
-    <row r="249" ht="15.0" customHeight="1"/>
-    <row r="250" ht="15.0" customHeight="1"/>
-    <row r="251" ht="15.0" customHeight="1"/>
-    <row r="252" ht="15.0" customHeight="1"/>
-    <row r="253" ht="15.0" customHeight="1"/>
-    <row r="254" ht="15.0" customHeight="1"/>
-    <row r="255" ht="15.0" customHeight="1"/>
-    <row r="256" ht="15.0" customHeight="1"/>
-    <row r="257" ht="15.0" customHeight="1"/>
-    <row r="258" ht="15.0" customHeight="1"/>
-    <row r="259" ht="15.0" customHeight="1"/>
-    <row r="260" ht="15.0" customHeight="1"/>
-    <row r="261" ht="15.0" customHeight="1"/>
-    <row r="262" ht="15.0" customHeight="1"/>
-    <row r="263" ht="15.0" customHeight="1"/>
-    <row r="264" ht="15.0" customHeight="1"/>
-    <row r="265" ht="15.0" customHeight="1"/>
-    <row r="266" ht="15.0" customHeight="1"/>
-    <row r="267" ht="15.0" customHeight="1"/>
-    <row r="268" ht="15.0" customHeight="1"/>
-    <row r="269" ht="15.0" customHeight="1"/>
-    <row r="270" ht="15.0" customHeight="1"/>
-    <row r="271" ht="15.0" customHeight="1"/>
-    <row r="272" ht="15.0" customHeight="1"/>
-    <row r="273" ht="15.0" customHeight="1"/>
-    <row r="274" ht="15.0" customHeight="1"/>
-    <row r="275" ht="15.0" customHeight="1"/>
-    <row r="276" ht="15.0" customHeight="1"/>
-    <row r="277" ht="15.0" customHeight="1"/>
-    <row r="278" ht="15.0" customHeight="1"/>
-    <row r="279" ht="15.0" customHeight="1"/>
-    <row r="280" ht="15.0" customHeight="1"/>
-    <row r="281" ht="15.0" customHeight="1"/>
-    <row r="282" ht="15.0" customHeight="1"/>
-    <row r="283" ht="15.0" customHeight="1"/>
-    <row r="284" ht="15.0" customHeight="1"/>
-    <row r="285" ht="15.0" customHeight="1"/>
-    <row r="286" ht="15.0" customHeight="1"/>
-    <row r="287" ht="15.0" customHeight="1"/>
-    <row r="288" ht="15.0" customHeight="1"/>
-    <row r="289" ht="15.0" customHeight="1"/>
-    <row r="290" ht="15.0" customHeight="1"/>
-    <row r="291" ht="15.0" customHeight="1"/>
-    <row r="292" ht="15.0" customHeight="1"/>
-    <row r="293" ht="15.0" customHeight="1"/>
-    <row r="294" ht="15.0" customHeight="1"/>
-    <row r="295" ht="15.0" customHeight="1"/>
-    <row r="296" ht="15.0" customHeight="1"/>
-    <row r="297" ht="15.0" customHeight="1"/>
-    <row r="298" ht="15.0" customHeight="1"/>
-    <row r="299" ht="15.0" customHeight="1"/>
-    <row r="300" ht="15.0" customHeight="1"/>
-    <row r="301" ht="15.0" customHeight="1"/>
-    <row r="302" ht="15.0" customHeight="1"/>
-    <row r="303" ht="15.0" customHeight="1"/>
-    <row r="304" ht="15.0" customHeight="1"/>
-    <row r="305" ht="15.0" customHeight="1"/>
-    <row r="306" ht="15.0" customHeight="1"/>
-    <row r="307" ht="15.0" customHeight="1"/>
-    <row r="308" ht="15.0" customHeight="1"/>
-    <row r="309" ht="15.0" customHeight="1"/>
-    <row r="310" ht="15.0" customHeight="1"/>
-    <row r="311" ht="15.0" customHeight="1"/>
-    <row r="312" ht="15.0" customHeight="1"/>
-    <row r="313" ht="15.0" customHeight="1"/>
-    <row r="314" ht="15.0" customHeight="1"/>
-    <row r="315" ht="15.0" customHeight="1"/>
-    <row r="316" ht="15.0" customHeight="1"/>
-    <row r="317" ht="15.0" customHeight="1"/>
-    <row r="318" ht="15.0" customHeight="1"/>
-    <row r="319" ht="15.0" customHeight="1"/>
-    <row r="320" ht="15.0" customHeight="1"/>
-    <row r="321" ht="15.0" customHeight="1"/>
-    <row r="322" ht="15.0" customHeight="1"/>
-    <row r="323" ht="15.0" customHeight="1"/>
-    <row r="324" ht="15.0" customHeight="1"/>
-    <row r="325" ht="15.0" customHeight="1"/>
-    <row r="326" ht="15.0" customHeight="1"/>
-    <row r="327" ht="15.0" customHeight="1"/>
-    <row r="328" ht="15.0" customHeight="1"/>
-    <row r="329" ht="15.0" customHeight="1"/>
-    <row r="330" ht="15.0" customHeight="1"/>
-    <row r="331" ht="15.0" customHeight="1"/>
-    <row r="332" ht="15.0" customHeight="1"/>
-    <row r="333" ht="15.0" customHeight="1"/>
-    <row r="334" ht="15.0" customHeight="1"/>
-    <row r="335" ht="15.0" customHeight="1"/>
-    <row r="336" ht="15.0" customHeight="1"/>
-    <row r="337" ht="15.0" customHeight="1"/>
-    <row r="338" ht="15.0" customHeight="1"/>
-    <row r="339" ht="15.0" customHeight="1"/>
-    <row r="340" ht="15.0" customHeight="1"/>
-    <row r="341" ht="15.0" customHeight="1"/>
-    <row r="342" ht="15.0" customHeight="1"/>
-    <row r="343" ht="15.0" customHeight="1"/>
-    <row r="344" ht="15.0" customHeight="1"/>
-    <row r="345" ht="15.0" customHeight="1"/>
-    <row r="346" ht="15.0" customHeight="1"/>
-    <row r="347" ht="15.0" customHeight="1"/>
-    <row r="348" ht="15.0" customHeight="1"/>
-    <row r="349" ht="15.0" customHeight="1"/>
-    <row r="350" ht="15.0" customHeight="1"/>
-    <row r="351" ht="15.0" customHeight="1"/>
-    <row r="352" ht="15.0" customHeight="1"/>
-    <row r="353" ht="15.0" customHeight="1"/>
-    <row r="354" ht="15.0" customHeight="1"/>
-    <row r="355" ht="15.0" customHeight="1"/>
-    <row r="356" ht="15.0" customHeight="1"/>
-    <row r="357" ht="15.0" customHeight="1"/>
-    <row r="358" ht="15.0" customHeight="1"/>
-    <row r="359" ht="15.0" customHeight="1"/>
-    <row r="360" ht="15.0" customHeight="1"/>
-    <row r="361" ht="15.0" customHeight="1"/>
-    <row r="362" ht="15.0" customHeight="1"/>
-    <row r="363" ht="15.0" customHeight="1"/>
-    <row r="364" ht="15.0" customHeight="1"/>
-    <row r="365" ht="15.0" customHeight="1"/>
-    <row r="366" ht="15.0" customHeight="1"/>
-    <row r="367" ht="15.0" customHeight="1"/>
-    <row r="368" ht="15.0" customHeight="1"/>
-    <row r="369" ht="15.0" customHeight="1"/>
-    <row r="370" ht="15.0" customHeight="1"/>
-    <row r="371" ht="15.0" customHeight="1"/>
-    <row r="372" ht="15.0" customHeight="1"/>
-    <row r="373" ht="15.0" customHeight="1"/>
-    <row r="374" ht="15.0" customHeight="1"/>
-    <row r="375" ht="15.0" customHeight="1"/>
-    <row r="376" ht="15.0" customHeight="1"/>
-    <row r="377" ht="15.0" customHeight="1"/>
-    <row r="378" ht="15.0" customHeight="1"/>
-    <row r="379" ht="15.0" customHeight="1"/>
-    <row r="380" ht="15.0" customHeight="1"/>
-    <row r="381" ht="15.0" customHeight="1"/>
-    <row r="382" ht="15.0" customHeight="1"/>
-    <row r="383" ht="15.0" customHeight="1"/>
-    <row r="384" ht="15.0" customHeight="1"/>
-    <row r="385" ht="15.0" customHeight="1"/>
-    <row r="386" ht="15.0" customHeight="1"/>
-    <row r="387" ht="15.0" customHeight="1"/>
-    <row r="388" ht="15.0" customHeight="1"/>
-    <row r="389" ht="15.0" customHeight="1"/>
-    <row r="390" ht="15.0" customHeight="1"/>
-    <row r="391" ht="15.0" customHeight="1"/>
-    <row r="392" ht="15.0" customHeight="1"/>
-    <row r="393" ht="15.0" customHeight="1"/>
-    <row r="394" ht="15.0" customHeight="1"/>
-    <row r="395" ht="15.0" customHeight="1"/>
-    <row r="396" ht="15.0" customHeight="1"/>
-    <row r="397" ht="15.0" customHeight="1"/>
-    <row r="398" ht="15.0" customHeight="1"/>
-    <row r="399" ht="15.0" customHeight="1"/>
-    <row r="400" ht="15.0" customHeight="1"/>
-    <row r="401" ht="15.0" customHeight="1"/>
-    <row r="402" ht="15.0" customHeight="1"/>
-    <row r="403" ht="15.0" customHeight="1"/>
-    <row r="404" ht="15.0" customHeight="1"/>
-    <row r="405" ht="15.0" customHeight="1"/>
-    <row r="406" ht="15.0" customHeight="1"/>
-    <row r="407" ht="15.0" customHeight="1"/>
-    <row r="408" ht="15.0" customHeight="1"/>
-    <row r="409" ht="15.0" customHeight="1"/>
-    <row r="410" ht="15.0" customHeight="1"/>
-    <row r="411" ht="15.0" customHeight="1"/>
-    <row r="412" ht="15.0" customHeight="1"/>
-    <row r="413" ht="15.0" customHeight="1"/>
-    <row r="414" ht="15.0" customHeight="1"/>
-    <row r="415" ht="15.0" customHeight="1"/>
-    <row r="416" ht="15.0" customHeight="1"/>
-    <row r="417" ht="15.0" customHeight="1"/>
-    <row r="418" ht="15.0" customHeight="1"/>
-    <row r="419" ht="15.0" customHeight="1"/>
-    <row r="420" ht="15.0" customHeight="1"/>
-    <row r="421" ht="15.0" customHeight="1"/>
-    <row r="422" ht="15.0" customHeight="1"/>
-    <row r="423" ht="15.0" customHeight="1"/>
-    <row r="424" ht="15.0" customHeight="1"/>
-    <row r="425" ht="15.0" customHeight="1"/>
-    <row r="426" ht="15.0" customHeight="1"/>
-    <row r="427" ht="15.0" customHeight="1"/>
-    <row r="428" ht="15.0" customHeight="1"/>
-    <row r="429" ht="15.0" customHeight="1"/>
-    <row r="430" ht="15.0" customHeight="1"/>
-    <row r="431" ht="15.0" customHeight="1"/>
-    <row r="432" ht="15.0" customHeight="1"/>
-    <row r="433" ht="15.0" customHeight="1"/>
-    <row r="434" ht="15.0" customHeight="1"/>
-    <row r="435" ht="15.0" customHeight="1"/>
-    <row r="436" ht="15.0" customHeight="1"/>
-    <row r="437" ht="15.0" customHeight="1"/>
-    <row r="438" ht="15.0" customHeight="1"/>
-    <row r="439" ht="15.0" customHeight="1"/>
-    <row r="440" ht="15.0" customHeight="1"/>
-    <row r="441" ht="15.0" customHeight="1"/>
-    <row r="442" ht="15.0" customHeight="1"/>
-    <row r="443" ht="15.0" customHeight="1"/>
-    <row r="444" ht="15.0" customHeight="1"/>
-    <row r="445" ht="15.0" customHeight="1"/>
-    <row r="446" ht="15.0" customHeight="1"/>
-    <row r="447" ht="15.0" customHeight="1"/>
-    <row r="448" ht="15.0" customHeight="1"/>
-    <row r="449" ht="15.0" customHeight="1"/>
-    <row r="450" ht="15.0" customHeight="1"/>
-    <row r="451" ht="15.0" customHeight="1"/>
-    <row r="452" ht="15.0" customHeight="1"/>
-    <row r="453" ht="15.0" customHeight="1"/>
-    <row r="454" ht="15.0" customHeight="1"/>
-    <row r="455" ht="15.0" customHeight="1"/>
-    <row r="456" ht="15.0" customHeight="1"/>
-    <row r="457" ht="15.0" customHeight="1"/>
-    <row r="458" ht="15.0" customHeight="1"/>
-    <row r="459" ht="15.0" customHeight="1"/>
-    <row r="460" ht="15.0" customHeight="1"/>
-    <row r="461" ht="15.0" customHeight="1"/>
-    <row r="462" ht="15.0" customHeight="1"/>
-    <row r="463" ht="15.0" customHeight="1"/>
-    <row r="464" ht="15.0" customHeight="1"/>
-    <row r="465" ht="15.0" customHeight="1"/>
-    <row r="466" ht="15.0" customHeight="1"/>
-    <row r="467" ht="15.0" customHeight="1"/>
-    <row r="468" ht="15.0" customHeight="1"/>
-    <row r="469" ht="15.0" customHeight="1"/>
-    <row r="470" ht="15.0" customHeight="1"/>
-    <row r="471" ht="15.0" customHeight="1"/>
-    <row r="472" ht="15.0" customHeight="1"/>
-    <row r="473" ht="15.0" customHeight="1"/>
-    <row r="474" ht="15.0" customHeight="1"/>
-    <row r="475" ht="15.0" customHeight="1"/>
-    <row r="476" ht="15.0" customHeight="1"/>
-    <row r="477" ht="15.0" customHeight="1"/>
-    <row r="478" ht="15.0" customHeight="1"/>
-    <row r="479" ht="15.0" customHeight="1"/>
-    <row r="480" ht="15.0" customHeight="1"/>
-    <row r="481" ht="15.0" customHeight="1"/>
-    <row r="482" ht="15.0" customHeight="1"/>
-    <row r="483" ht="15.0" customHeight="1"/>
-    <row r="484" ht="15.0" customHeight="1"/>
-    <row r="485" ht="15.0" customHeight="1"/>
-    <row r="486" ht="15.0" customHeight="1"/>
-    <row r="487" ht="15.0" customHeight="1"/>
-    <row r="488" ht="15.0" customHeight="1"/>
-    <row r="489" ht="15.0" customHeight="1"/>
-    <row r="490" ht="15.0" customHeight="1"/>
-    <row r="491" ht="15.0" customHeight="1"/>
-    <row r="492" ht="15.0" customHeight="1"/>
-    <row r="493" ht="15.0" customHeight="1"/>
-    <row r="494" ht="15.0" customHeight="1"/>
-    <row r="495" ht="15.0" customHeight="1"/>
-    <row r="496" ht="15.0" customHeight="1"/>
-    <row r="497" ht="15.0" customHeight="1"/>
-    <row r="498" ht="15.0" customHeight="1"/>
-    <row r="499" ht="15.0" customHeight="1"/>
-    <row r="500" ht="15.0" customHeight="1"/>
-    <row r="501" ht="15.0" customHeight="1"/>
-    <row r="502" ht="15.0" customHeight="1"/>
-    <row r="503" ht="15.0" customHeight="1"/>
-    <row r="504" ht="15.0" customHeight="1"/>
-    <row r="505" ht="15.0" customHeight="1"/>
-    <row r="506" ht="15.0" customHeight="1"/>
-    <row r="507" ht="15.0" customHeight="1"/>
-    <row r="508" ht="15.0" customHeight="1"/>
-    <row r="509" ht="15.0" customHeight="1"/>
-    <row r="510" ht="15.0" customHeight="1"/>
-    <row r="511" ht="15.0" customHeight="1"/>
-    <row r="512" ht="15.0" customHeight="1"/>
-    <row r="513" ht="15.0" customHeight="1"/>
-    <row r="514" ht="15.0" customHeight="1"/>
-    <row r="515" ht="15.0" customHeight="1"/>
-    <row r="516" ht="15.0" customHeight="1"/>
-    <row r="517" ht="15.0" customHeight="1"/>
-    <row r="518" ht="15.0" customHeight="1"/>
-    <row r="519" ht="15.0" customHeight="1"/>
-    <row r="520" ht="15.0" customHeight="1"/>
-    <row r="521" ht="15.0" customHeight="1"/>
-    <row r="522" ht="15.0" customHeight="1"/>
-    <row r="523" ht="15.0" customHeight="1"/>
-    <row r="524" ht="15.0" customHeight="1"/>
-    <row r="525" ht="15.0" customHeight="1"/>
-    <row r="526" ht="15.0" customHeight="1"/>
-    <row r="527" ht="15.0" customHeight="1"/>
-    <row r="528" ht="15.0" customHeight="1"/>
-    <row r="529" ht="15.0" customHeight="1"/>
-    <row r="530" ht="15.0" customHeight="1"/>
-    <row r="531" ht="15.0" customHeight="1"/>
-    <row r="532" ht="15.0" customHeight="1"/>
-    <row r="533" ht="15.0" customHeight="1"/>
-    <row r="534" ht="15.0" customHeight="1"/>
-    <row r="535" ht="15.0" customHeight="1"/>
-    <row r="536" ht="15.0" customHeight="1"/>
-    <row r="537" ht="15.0" customHeight="1"/>
-    <row r="538" ht="15.0" customHeight="1"/>
-    <row r="539" ht="15.0" customHeight="1"/>
-    <row r="540" ht="15.0" customHeight="1"/>
-    <row r="541" ht="15.0" customHeight="1"/>
-    <row r="542" ht="15.0" customHeight="1"/>
-    <row r="543" ht="15.0" customHeight="1"/>
-    <row r="544" ht="15.0" customHeight="1"/>
-    <row r="545" ht="15.0" customHeight="1"/>
-    <row r="546" ht="15.0" customHeight="1"/>
-    <row r="547" ht="15.0" customHeight="1"/>
-    <row r="548" ht="15.0" customHeight="1"/>
-    <row r="549" ht="15.0" customHeight="1"/>
-    <row r="550" ht="15.0" customHeight="1"/>
-    <row r="551" ht="15.0" customHeight="1"/>
-    <row r="552" ht="15.0" customHeight="1"/>
-    <row r="553" ht="15.0" customHeight="1"/>
-    <row r="554" ht="15.0" customHeight="1"/>
-    <row r="555" ht="15.0" customHeight="1"/>
-    <row r="556" ht="15.0" customHeight="1"/>
-    <row r="557" ht="15.0" customHeight="1"/>
-    <row r="558" ht="15.0" customHeight="1"/>
-    <row r="559" ht="15.0" customHeight="1"/>
-    <row r="560" ht="15.0" customHeight="1"/>
-    <row r="561" ht="15.0" customHeight="1"/>
-    <row r="562" ht="15.0" customHeight="1"/>
-    <row r="563" ht="15.0" customHeight="1"/>
-    <row r="564" ht="15.0" customHeight="1"/>
-    <row r="565" ht="15.0" customHeight="1"/>
-    <row r="566" ht="15.0" customHeight="1"/>
-    <row r="567" ht="15.0" customHeight="1"/>
-    <row r="568" ht="15.0" customHeight="1"/>
-    <row r="569" ht="15.0" customHeight="1"/>
-    <row r="570" ht="15.0" customHeight="1"/>
-    <row r="571" ht="15.0" customHeight="1"/>
-    <row r="572" ht="15.0" customHeight="1"/>
-    <row r="573" ht="15.0" customHeight="1"/>
-    <row r="574" ht="15.0" customHeight="1"/>
-    <row r="575" ht="15.0" customHeight="1"/>
-    <row r="576" ht="15.0" customHeight="1"/>
-    <row r="577" ht="15.0" customHeight="1"/>
-    <row r="578" ht="15.0" customHeight="1"/>
-    <row r="579" ht="15.0" customHeight="1"/>
-    <row r="580" ht="15.0" customHeight="1"/>
-    <row r="581" ht="15.0" customHeight="1"/>
-    <row r="582" ht="15.0" customHeight="1"/>
-    <row r="583" ht="15.0" customHeight="1"/>
-    <row r="584" ht="15.0" customHeight="1"/>
-    <row r="585" ht="15.0" customHeight="1"/>
-    <row r="586" ht="15.0" customHeight="1"/>
-    <row r="587" ht="15.0" customHeight="1"/>
-    <row r="588" ht="15.0" customHeight="1"/>
-    <row r="589" ht="15.0" customHeight="1"/>
-    <row r="590" ht="15.0" customHeight="1"/>
-    <row r="591" ht="15.0" customHeight="1"/>
-    <row r="592" ht="15.0" customHeight="1"/>
-    <row r="593" ht="15.0" customHeight="1"/>
-    <row r="594" ht="15.0" customHeight="1"/>
-    <row r="595" ht="15.0" customHeight="1"/>
-    <row r="596" ht="15.0" customHeight="1"/>
-    <row r="597" ht="15.0" customHeight="1"/>
-    <row r="598" ht="15.0" customHeight="1"/>
-    <row r="599" ht="15.0" customHeight="1"/>
-    <row r="600" ht="15.0" customHeight="1"/>
-    <row r="601" ht="15.0" customHeight="1"/>
-    <row r="602" ht="15.0" customHeight="1"/>
-    <row r="603" ht="15.0" customHeight="1"/>
-    <row r="604" ht="15.0" customHeight="1"/>
-    <row r="605" ht="15.0" customHeight="1"/>
-    <row r="606" ht="15.0" customHeight="1"/>
-    <row r="607" ht="15.0" customHeight="1"/>
-    <row r="608" ht="15.0" customHeight="1"/>
-    <row r="609" ht="15.0" customHeight="1"/>
-    <row r="610" ht="15.0" customHeight="1"/>
-    <row r="611" ht="15.0" customHeight="1"/>
-    <row r="612" ht="15.0" customHeight="1"/>
-    <row r="613" ht="15.0" customHeight="1"/>
-    <row r="614" ht="15.0" customHeight="1"/>
-    <row r="615" ht="15.0" customHeight="1"/>
-    <row r="616" ht="15.0" customHeight="1"/>
-    <row r="617" ht="15.0" customHeight="1"/>
-    <row r="618" ht="15.0" customHeight="1"/>
-    <row r="619" ht="15.0" customHeight="1"/>
-    <row r="620" ht="15.0" customHeight="1"/>
-    <row r="621" ht="15.0" customHeight="1"/>
-    <row r="622" ht="15.0" customHeight="1"/>
-    <row r="623" ht="15.0" customHeight="1"/>
-    <row r="624" ht="15.0" customHeight="1"/>
-    <row r="625" ht="15.0" customHeight="1"/>
-    <row r="626" ht="15.0" customHeight="1"/>
-    <row r="627" ht="15.0" customHeight="1"/>
-    <row r="628" ht="15.0" customHeight="1"/>
-    <row r="629" ht="15.0" customHeight="1"/>
-    <row r="630" ht="15.0" customHeight="1"/>
-    <row r="631" ht="15.0" customHeight="1"/>
-    <row r="632" ht="15.0" customHeight="1"/>
-    <row r="633" ht="15.0" customHeight="1"/>
-    <row r="634" ht="15.0" customHeight="1"/>
-    <row r="635" ht="15.0" customHeight="1"/>
-    <row r="636" ht="15.0" customHeight="1"/>
-    <row r="637" ht="15.0" customHeight="1"/>
-    <row r="638" ht="15.0" customHeight="1"/>
-    <row r="639" ht="15.0" customHeight="1"/>
-    <row r="640" ht="15.0" customHeight="1"/>
-    <row r="641" ht="15.0" customHeight="1"/>
-    <row r="642" ht="15.0" customHeight="1"/>
-    <row r="643" ht="15.0" customHeight="1"/>
-    <row r="644" ht="15.0" customHeight="1"/>
-    <row r="645" ht="15.0" customHeight="1"/>
-    <row r="646" ht="15.0" customHeight="1"/>
-    <row r="647" ht="15.0" customHeight="1"/>
-    <row r="648" ht="15.0" customHeight="1"/>
-    <row r="649" ht="15.0" customHeight="1"/>
-    <row r="650" ht="15.0" customHeight="1"/>
-    <row r="651" ht="15.0" customHeight="1"/>
-    <row r="652" ht="15.0" customHeight="1"/>
-    <row r="653" ht="15.0" customHeight="1"/>
-    <row r="654" ht="15.0" customHeight="1"/>
-    <row r="655" ht="15.0" customHeight="1"/>
-    <row r="656" ht="15.0" customHeight="1"/>
-    <row r="657" ht="15.0" customHeight="1"/>
-    <row r="658" ht="15.0" customHeight="1"/>
-    <row r="659" ht="15.0" customHeight="1"/>
-    <row r="660" ht="15.0" customHeight="1"/>
-    <row r="661" ht="15.0" customHeight="1"/>
-    <row r="662" ht="15.0" customHeight="1"/>
-    <row r="663" ht="15.0" customHeight="1"/>
-    <row r="664" ht="15.0" customHeight="1"/>
-    <row r="665" ht="15.0" customHeight="1"/>
-    <row r="666" ht="15.0" customHeight="1"/>
-    <row r="667" ht="15.0" customHeight="1"/>
-    <row r="668" ht="15.0" customHeight="1"/>
-    <row r="669" ht="15.0" customHeight="1"/>
-    <row r="670" ht="15.0" customHeight="1"/>
-    <row r="671" ht="15.0" customHeight="1"/>
-    <row r="672" ht="15.0" customHeight="1"/>
-    <row r="673" ht="15.0" customHeight="1"/>
-    <row r="674" ht="15.0" customHeight="1"/>
-    <row r="675" ht="15.0" customHeight="1"/>
-    <row r="676" ht="15.0" customHeight="1"/>
-    <row r="677" ht="15.0" customHeight="1"/>
-    <row r="678" ht="15.0" customHeight="1"/>
-    <row r="679" ht="15.0" customHeight="1"/>
-    <row r="680" ht="15.0" customHeight="1"/>
-    <row r="681" ht="15.0" customHeight="1"/>
-    <row r="682" ht="15.0" customHeight="1"/>
-    <row r="683" ht="15.0" customHeight="1"/>
-    <row r="684" ht="15.0" customHeight="1"/>
-    <row r="685" ht="15.0" customHeight="1"/>
-    <row r="686" ht="15.0" customHeight="1"/>
-    <row r="687" ht="15.0" customHeight="1"/>
-    <row r="688" ht="15.0" customHeight="1"/>
-    <row r="689" ht="15.0" customHeight="1"/>
-    <row r="690" ht="15.0" customHeight="1"/>
-    <row r="691" ht="15.0" customHeight="1"/>
-    <row r="692" ht="15.0" customHeight="1"/>
-    <row r="693" ht="15.0" customHeight="1"/>
-    <row r="694" ht="15.0" customHeight="1"/>
-    <row r="695" ht="15.0" customHeight="1"/>
-    <row r="696" ht="15.0" customHeight="1"/>
-    <row r="697" ht="15.0" customHeight="1"/>
-    <row r="698" ht="15.0" customHeight="1"/>
-    <row r="699" ht="15.0" customHeight="1"/>
-    <row r="700" ht="15.0" customHeight="1"/>
-    <row r="701" ht="15.0" customHeight="1"/>
-    <row r="702" ht="15.0" customHeight="1"/>
-    <row r="703" ht="15.0" customHeight="1"/>
-    <row r="704" ht="15.0" customHeight="1"/>
-    <row r="705" ht="15.0" customHeight="1"/>
-    <row r="706" ht="15.0" customHeight="1"/>
-    <row r="707" ht="15.0" customHeight="1"/>
-    <row r="708" ht="15.0" customHeight="1"/>
-    <row r="709" ht="15.0" customHeight="1"/>
-    <row r="710" ht="15.0" customHeight="1"/>
-    <row r="711" ht="15.0" customHeight="1"/>
-    <row r="712" ht="15.0" customHeight="1"/>
-    <row r="713" ht="15.0" customHeight="1"/>
-    <row r="714" ht="15.0" customHeight="1"/>
-    <row r="715" ht="15.0" customHeight="1"/>
-    <row r="716" ht="15.0" customHeight="1"/>
-    <row r="717" ht="15.0" customHeight="1"/>
-    <row r="718" ht="15.0" customHeight="1"/>
-    <row r="719" ht="15.0" customHeight="1"/>
-    <row r="720" ht="15.0" customHeight="1"/>
-    <row r="721" ht="15.0" customHeight="1"/>
-    <row r="722" ht="15.0" customHeight="1"/>
-    <row r="723" ht="15.0" customHeight="1"/>
-    <row r="724" ht="15.0" customHeight="1"/>
-    <row r="725" ht="15.0" customHeight="1"/>
-    <row r="726" ht="15.0" customHeight="1"/>
-    <row r="727" ht="15.0" customHeight="1"/>
-    <row r="728" ht="15.0" customHeight="1"/>
-    <row r="729" ht="15.0" customHeight="1"/>
-    <row r="730" ht="15.0" customHeight="1"/>
-    <row r="731" ht="15.0" customHeight="1"/>
-    <row r="732" ht="15.0" customHeight="1"/>
-    <row r="733" ht="15.0" customHeight="1"/>
-    <row r="734" ht="15.0" customHeight="1"/>
-    <row r="735" ht="15.0" customHeight="1"/>
-    <row r="736" ht="15.0" customHeight="1"/>
-    <row r="737" ht="15.0" customHeight="1"/>
-    <row r="738" ht="15.0" customHeight="1"/>
-    <row r="739" ht="15.0" customHeight="1"/>
-    <row r="740" ht="15.0" customHeight="1"/>
-    <row r="741" ht="15.0" customHeight="1"/>
-    <row r="742" ht="15.0" customHeight="1"/>
-    <row r="743" ht="15.0" customHeight="1"/>
-    <row r="744" ht="15.0" customHeight="1"/>
-    <row r="745" ht="15.0" customHeight="1"/>
-    <row r="746" ht="15.0" customHeight="1"/>
-    <row r="747" ht="15.0" customHeight="1"/>
-    <row r="748" ht="15.0" customHeight="1"/>
-    <row r="749" ht="15.0" customHeight="1"/>
-    <row r="750" ht="15.0" customHeight="1"/>
-    <row r="751" ht="15.0" customHeight="1"/>
-    <row r="752" ht="15.0" customHeight="1"/>
-    <row r="753" ht="15.0" customHeight="1"/>
-    <row r="754" ht="15.0" customHeight="1"/>
-    <row r="755" ht="15.0" customHeight="1"/>
-    <row r="756" ht="15.0" customHeight="1"/>
-    <row r="757" ht="15.0" customHeight="1"/>
-    <row r="758" ht="15.0" customHeight="1"/>
-    <row r="759" ht="15.0" customHeight="1"/>
-    <row r="760" ht="15.0" customHeight="1"/>
-    <row r="761" ht="15.0" customHeight="1"/>
-    <row r="762" ht="15.0" customHeight="1"/>
-    <row r="763" ht="15.0" customHeight="1"/>
-    <row r="764" ht="15.0" customHeight="1"/>
-    <row r="765" ht="15.0" customHeight="1"/>
-    <row r="766" ht="15.0" customHeight="1"/>
-    <row r="767" ht="15.0" customHeight="1"/>
-    <row r="768" ht="15.0" customHeight="1"/>
-    <row r="769" ht="15.0" customHeight="1"/>
-    <row r="770" ht="15.0" customHeight="1"/>
-    <row r="771" ht="15.0" customHeight="1"/>
-    <row r="772" ht="15.0" customHeight="1"/>
-    <row r="773" ht="15.0" customHeight="1"/>
-    <row r="774" ht="15.0" customHeight="1"/>
-    <row r="775" ht="15.0" customHeight="1"/>
-    <row r="776" ht="15.0" customHeight="1"/>
-    <row r="777" ht="15.0" customHeight="1"/>
-    <row r="778" ht="15.0" customHeight="1"/>
-    <row r="779" ht="15.0" customHeight="1"/>
-    <row r="780" ht="15.0" customHeight="1"/>
-    <row r="781" ht="15.0" customHeight="1"/>
-    <row r="782" ht="15.0" customHeight="1"/>
-    <row r="783" ht="15.0" customHeight="1"/>
-    <row r="784" ht="15.0" customHeight="1"/>
-    <row r="785" ht="15.0" customHeight="1"/>
-    <row r="786" ht="15.0" customHeight="1"/>
-    <row r="787" ht="15.0" customHeight="1"/>
-    <row r="788" ht="15.0" customHeight="1"/>
-    <row r="789" ht="15.0" customHeight="1"/>
-    <row r="790" ht="15.0" customHeight="1"/>
-    <row r="791" ht="15.0" customHeight="1"/>
-    <row r="792" ht="15.0" customHeight="1"/>
-    <row r="793" ht="15.0" customHeight="1"/>
-    <row r="794" ht="15.0" customHeight="1"/>
-    <row r="795" ht="15.0" customHeight="1"/>
-    <row r="796" ht="15.0" customHeight="1"/>
-    <row r="797" ht="15.0" customHeight="1"/>
-    <row r="798" ht="15.0" customHeight="1"/>
-    <row r="799" ht="15.0" customHeight="1"/>
-    <row r="800" ht="15.0" customHeight="1"/>
-    <row r="801" ht="15.0" customHeight="1"/>
-    <row r="802" ht="15.0" customHeight="1"/>
-    <row r="803" ht="15.0" customHeight="1"/>
-    <row r="804" ht="15.0" customHeight="1"/>
-    <row r="805" ht="15.0" customHeight="1"/>
-    <row r="806" ht="15.0" customHeight="1"/>
-    <row r="807" ht="15.0" customHeight="1"/>
-    <row r="808" ht="15.0" customHeight="1"/>
-    <row r="809" ht="15.0" customHeight="1"/>
-    <row r="810" ht="15.0" customHeight="1"/>
-    <row r="811" ht="15.0" customHeight="1"/>
-    <row r="812" ht="15.0" customHeight="1"/>
-    <row r="813" ht="15.0" customHeight="1"/>
-    <row r="814" ht="15.0" customHeight="1"/>
-    <row r="815" ht="15.0" customHeight="1"/>
-    <row r="816" ht="15.0" customHeight="1"/>
-    <row r="817" ht="15.0" customHeight="1"/>
-    <row r="818" ht="15.0" customHeight="1"/>
-    <row r="819" ht="15.0" customHeight="1"/>
-    <row r="820" ht="15.0" customHeight="1"/>
-    <row r="821" ht="15.0" customHeight="1"/>
-    <row r="822" ht="15.0" customHeight="1"/>
-    <row r="823" ht="15.0" customHeight="1"/>
-    <row r="824" ht="15.0" customHeight="1"/>
-    <row r="825" ht="15.0" customHeight="1"/>
-    <row r="826" ht="15.0" customHeight="1"/>
-    <row r="827" ht="15.0" customHeight="1"/>
-    <row r="828" ht="15.0" customHeight="1"/>
-    <row r="829" ht="15.0" customHeight="1"/>
-    <row r="830" ht="15.0" customHeight="1"/>
-    <row r="831" ht="15.0" customHeight="1"/>
-    <row r="832" ht="15.0" customHeight="1"/>
-    <row r="833" ht="15.0" customHeight="1"/>
-    <row r="834" ht="15.0" customHeight="1"/>
-    <row r="835" ht="15.0" customHeight="1"/>
-    <row r="836" ht="15.0" customHeight="1"/>
-    <row r="837" ht="15.0" customHeight="1"/>
-    <row r="838" ht="15.0" customHeight="1"/>
-    <row r="839" ht="15.0" customHeight="1"/>
-    <row r="840" ht="15.0" customHeight="1"/>
-    <row r="841" ht="15.0" customHeight="1"/>
-    <row r="842" ht="15.0" customHeight="1"/>
-    <row r="843" ht="15.0" customHeight="1"/>
-    <row r="844" ht="15.0" customHeight="1"/>
-    <row r="845" ht="15.0" customHeight="1"/>
-    <row r="846" ht="15.0" customHeight="1"/>
-    <row r="847" ht="15.0" customHeight="1"/>
-    <row r="848" ht="15.0" customHeight="1"/>
-    <row r="849" ht="15.0" customHeight="1"/>
-    <row r="850" ht="15.0" customHeight="1"/>
-    <row r="851" ht="15.0" customHeight="1"/>
-    <row r="852" ht="15.0" customHeight="1"/>
-    <row r="853" ht="15.0" customHeight="1"/>
-    <row r="854" ht="15.0" customHeight="1"/>
-    <row r="855" ht="15.0" customHeight="1"/>
-    <row r="856" ht="15.0" customHeight="1"/>
-    <row r="857" ht="15.0" customHeight="1"/>
-    <row r="858" ht="15.0" customHeight="1"/>
-    <row r="859" ht="15.0" customHeight="1"/>
-    <row r="860" ht="15.0" customHeight="1"/>
-    <row r="861" ht="15.0" customHeight="1"/>
-    <row r="862" ht="15.0" customHeight="1"/>
-    <row r="863" ht="15.0" customHeight="1"/>
-    <row r="864" ht="15.0" customHeight="1"/>
-    <row r="865" ht="15.0" customHeight="1"/>
-    <row r="866" ht="15.0" customHeight="1"/>
-    <row r="867" ht="15.0" customHeight="1"/>
-    <row r="868" ht="15.0" customHeight="1"/>
-    <row r="869" ht="15.0" customHeight="1"/>
-    <row r="870" ht="15.0" customHeight="1"/>
-    <row r="871" ht="15.0" customHeight="1"/>
-    <row r="872" ht="15.0" customHeight="1"/>
-    <row r="873" ht="15.0" customHeight="1"/>
-    <row r="874" ht="15.0" customHeight="1"/>
-    <row r="875" ht="15.0" customHeight="1"/>
-    <row r="876" ht="15.0" customHeight="1"/>
-    <row r="877" ht="15.0" customHeight="1"/>
-    <row r="878" ht="15.0" customHeight="1"/>
-    <row r="879" ht="15.0" customHeight="1"/>
-    <row r="880" ht="15.0" customHeight="1"/>
-    <row r="881" ht="15.0" customHeight="1"/>
-    <row r="882" ht="15.0" customHeight="1"/>
-    <row r="883" ht="15.0" customHeight="1"/>
-    <row r="884" ht="15.0" customHeight="1"/>
-    <row r="885" ht="15.0" customHeight="1"/>
-    <row r="886" ht="15.0" customHeight="1"/>
-    <row r="887" ht="15.0" customHeight="1"/>
-    <row r="888" ht="15.0" customHeight="1"/>
-    <row r="889" ht="15.0" customHeight="1"/>
-    <row r="890" ht="15.0" customHeight="1"/>
-    <row r="891" ht="15.0" customHeight="1"/>
-    <row r="892" ht="15.0" customHeight="1"/>
-    <row r="893" ht="15.0" customHeight="1"/>
-    <row r="894" ht="15.0" customHeight="1"/>
-    <row r="895" ht="15.0" customHeight="1"/>
-    <row r="896" ht="15.0" customHeight="1"/>
-    <row r="897" ht="15.0" customHeight="1"/>
-    <row r="898" ht="15.0" customHeight="1"/>
-    <row r="899" ht="15.0" customHeight="1"/>
-    <row r="900" ht="15.0" customHeight="1"/>
-    <row r="901" ht="15.0" customHeight="1"/>
-    <row r="902" ht="15.0" customHeight="1"/>
-    <row r="903" ht="15.0" customHeight="1"/>
-    <row r="904" ht="15.0" customHeight="1"/>
-    <row r="905" ht="15.0" customHeight="1"/>
-    <row r="906" ht="15.0" customHeight="1"/>
-    <row r="907" ht="15.0" customHeight="1"/>
-    <row r="908" ht="15.0" customHeight="1"/>
-    <row r="909" ht="15.0" customHeight="1"/>
-    <row r="910" ht="15.0" customHeight="1"/>
-    <row r="911" ht="15.0" customHeight="1"/>
-    <row r="912" ht="15.0" customHeight="1"/>
-    <row r="913" ht="15.0" customHeight="1"/>
-    <row r="914" ht="15.0" customHeight="1"/>
-    <row r="915" ht="15.0" customHeight="1"/>
-    <row r="916" ht="15.0" customHeight="1"/>
-    <row r="917" ht="15.0" customHeight="1"/>
-    <row r="918" ht="15.0" customHeight="1"/>
-    <row r="919" ht="15.0" customHeight="1"/>
-    <row r="920" ht="15.0" customHeight="1"/>
-    <row r="921" ht="15.0" customHeight="1"/>
-    <row r="922" ht="15.0" customHeight="1"/>
-    <row r="923" ht="15.0" customHeight="1"/>
-    <row r="924" ht="15.0" customHeight="1"/>
-    <row r="925" ht="15.0" customHeight="1"/>
-    <row r="926" ht="15.0" customHeight="1"/>
-    <row r="927" ht="15.0" customHeight="1"/>
-    <row r="928" ht="15.0" customHeight="1"/>
-    <row r="929" ht="15.0" customHeight="1"/>
-    <row r="930" ht="15.0" customHeight="1"/>
-    <row r="931" ht="15.0" customHeight="1"/>
-    <row r="932" ht="15.0" customHeight="1"/>
-    <row r="933" ht="15.0" customHeight="1"/>
-    <row r="934" ht="15.0" customHeight="1"/>
-    <row r="935" ht="15.0" customHeight="1"/>
-    <row r="936" ht="15.0" customHeight="1"/>
-    <row r="937" ht="15.0" customHeight="1"/>
-    <row r="938" ht="15.0" customHeight="1"/>
-    <row r="939" ht="15.0" customHeight="1"/>
-    <row r="940" ht="15.0" customHeight="1"/>
-    <row r="941" ht="15.0" customHeight="1"/>
-    <row r="942" ht="15.0" customHeight="1"/>
-    <row r="943" ht="15.0" customHeight="1"/>
-    <row r="944" ht="15.0" customHeight="1"/>
-    <row r="945" ht="15.0" customHeight="1"/>
-    <row r="946" ht="15.0" customHeight="1"/>
-    <row r="947" ht="15.0" customHeight="1"/>
-    <row r="948" ht="15.0" customHeight="1"/>
-    <row r="949" ht="15.0" customHeight="1"/>
-    <row r="950" ht="15.0" customHeight="1"/>
-    <row r="951" ht="15.0" customHeight="1"/>
-    <row r="952" ht="15.0" customHeight="1"/>
-    <row r="953" ht="15.0" customHeight="1"/>
-    <row r="954" ht="15.0" customHeight="1"/>
-    <row r="955" ht="15.0" customHeight="1"/>
-    <row r="956" ht="15.0" customHeight="1"/>
-    <row r="957" ht="15.0" customHeight="1"/>
-    <row r="958" ht="15.0" customHeight="1"/>
-    <row r="959" ht="15.0" customHeight="1"/>
-    <row r="960" ht="15.0" customHeight="1"/>
-    <row r="961" ht="15.0" customHeight="1"/>
-    <row r="962" ht="15.0" customHeight="1"/>
-    <row r="963" ht="15.0" customHeight="1"/>
-    <row r="964" ht="15.0" customHeight="1"/>
-    <row r="965" ht="15.0" customHeight="1"/>
-    <row r="966" ht="15.0" customHeight="1"/>
-    <row r="967" ht="15.0" customHeight="1"/>
-    <row r="968" ht="15.0" customHeight="1"/>
-    <row r="969" ht="15.0" customHeight="1"/>
-    <row r="970" ht="15.0" customHeight="1"/>
-    <row r="971" ht="15.0" customHeight="1"/>
-    <row r="972" ht="15.0" customHeight="1"/>
-    <row r="973" ht="15.0" customHeight="1"/>
-    <row r="974" ht="15.0" customHeight="1"/>
-    <row r="975" ht="15.0" customHeight="1"/>
-    <row r="976" ht="15.0" customHeight="1"/>
-    <row r="977" ht="15.0" customHeight="1"/>
-    <row r="978" ht="15.0" customHeight="1"/>
-    <row r="979" ht="15.0" customHeight="1"/>
-    <row r="980" ht="15.0" customHeight="1"/>
-    <row r="981" ht="15.0" customHeight="1"/>
-    <row r="982" ht="15.0" customHeight="1"/>
-    <row r="983" ht="15.0" customHeight="1"/>
-    <row r="984" ht="15.0" customHeight="1"/>
-    <row r="985" ht="15.0" customHeight="1"/>
-    <row r="986" ht="15.0" customHeight="1"/>
-    <row r="987" ht="15.0" customHeight="1"/>
-    <row r="988" ht="15.0" customHeight="1"/>
-    <row r="989" ht="15.0" customHeight="1"/>
-    <row r="990" ht="15.0" customHeight="1"/>
-    <row r="991" ht="15.0" customHeight="1"/>
-    <row r="992" ht="15.0" customHeight="1"/>
-    <row r="993" ht="15.0" customHeight="1"/>
-    <row r="994" ht="15.0" customHeight="1"/>
-    <row r="995" ht="15.0" customHeight="1"/>
-    <row r="996" ht="15.0" customHeight="1"/>
-    <row r="997" ht="15.0" customHeight="1"/>
-    <row r="998" ht="15.0" customHeight="1"/>
-    <row r="999" ht="15.0" customHeight="1"/>
-    <row r="1000" ht="15.0" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/ValueInfo/T_ValTable.xlsx
+++ b/Templates/Tables/ValueInfo/T_ValTable.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>ID</t>
   </si>
@@ -75,60 +75,12 @@
   <si>
     <t>휴대용 콘솔 플랫폼 타겟 프레임</t>
   </si>
-  <si>
-    <t>OFFSET_V_ALERT_P_TITLE</t>
-  </si>
-  <si>
-    <t>경고 팝업 타이틀 수직 간격</t>
-  </si>
-  <si>
-    <t>OFFSET_V_ALERT_P_BTN</t>
-  </si>
-  <si>
-    <t>경고 팝업 버튼 수직 간격</t>
-  </si>
-  <si>
-    <t>OFFSET_H_ALERT_P_BTN</t>
-  </si>
-  <si>
-    <t>경고 팝업 버튼 수평 간격</t>
-  </si>
-  <si>
-    <t>EXTRA_OFFSET_V_ALERT_P_TITLE</t>
-  </si>
-  <si>
-    <t>경고 팝업 타이틀 추가 수직 간격</t>
-  </si>
-  <si>
-    <t>EXTRA_OFFSET_V_ALERT_P_MSG</t>
-  </si>
-  <si>
-    <t>경고 팝업 메세지 추가 수직 간격</t>
-  </si>
-  <si>
-    <t>EXTRA_OFFSET_V_ALERT_P_BTN</t>
-  </si>
-  <si>
-    <t>경고 팝업 버튼 추가 수직 간격</t>
-  </si>
-  <si>
-    <t>OFFSET_V_ALERT_P_BG</t>
-  </si>
-  <si>
-    <t>경고 팝업 배경 수직 간격</t>
-  </si>
-  <si>
-    <t>OFFSET_H_ALERT_P_BG</t>
-  </si>
-  <si>
-    <t>경고 팝업 배경 수평 간격</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -137,6 +89,10 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -153,7 +109,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border/>
     <border>
       <left style="thin">
@@ -169,9 +125,22 @@
       </top>
     </border>
     <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
     </border>
     <border>
       <left style="thin">
@@ -186,21 +155,32 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -493,561 +473,489 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
+      <c r="Z2" s="4"/>
     </row>
     <row r="3" ht="15.0" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="6">
         <v>0.0</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="6">
         <v>10.0</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="6">
         <v>2.0</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="7"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="6">
         <v>0.0</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="6">
         <v>6.0</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="6">
         <v>1.0</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="7"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="6">
         <v>0.0</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="6">
         <v>0.0</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="6">
         <v>1.0</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="6"/>
+      <c r="Z5" s="7"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="6">
         <v>0.0</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="6">
         <v>60.0</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="6">
         <v>1.0</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="7"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="6">
         <v>0.0</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="6">
         <v>60.0</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="6">
         <v>1.0</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="7"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="6">
         <v>0.0</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
         <v>60.0</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="6">
         <v>1.0</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="7"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="9">
         <v>0.0</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="9">
         <v>60.0</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="9">
         <v>1.0</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
-      <c r="W9" s="5"/>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="10"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C10" s="5">
-        <v>70.0</v>
-      </c>
-      <c r="D10" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
     </row>
     <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C11" s="5">
-        <v>45.0</v>
-      </c>
-      <c r="D11" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
     </row>
     <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C12" s="5">
-        <v>45.0</v>
-      </c>
-      <c r="D12" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
     </row>
     <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C13" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="D13" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="5"/>
-      <c r="X13" s="5"/>
-      <c r="Y13" s="5"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
     </row>
     <row r="14" ht="15.0" customHeight="1">
-      <c r="A14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C14" s="5">
-        <v>10.0</v>
-      </c>
-      <c r="D14" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="5"/>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
     </row>
     <row r="15" ht="15.0" customHeight="1">
-      <c r="A15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C15" s="5">
-        <v>15.0</v>
-      </c>
-      <c r="D15" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
-      <c r="V15" s="5"/>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
     </row>
     <row r="16" ht="15.0" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="C16" s="5">
-        <v>45.0</v>
-      </c>
-      <c r="D16" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="5"/>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5"/>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="5"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1"/>
     </row>
     <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="C17" s="7">
-        <v>145.0</v>
-      </c>
-      <c r="D17" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1"/>
@@ -6314,222 +6222,14 @@
       <c r="X212" s="1"/>
       <c r="Y212" s="1"/>
     </row>
-    <row r="213" ht="15.0" customHeight="1">
-      <c r="A213" s="1"/>
-      <c r="B213" s="1"/>
-      <c r="C213" s="1"/>
-      <c r="D213" s="1"/>
-      <c r="E213" s="1"/>
-      <c r="F213" s="1"/>
-      <c r="G213" s="1"/>
-      <c r="H213" s="1"/>
-      <c r="I213" s="1"/>
-      <c r="J213" s="1"/>
-      <c r="K213" s="1"/>
-      <c r="L213" s="1"/>
-      <c r="M213" s="1"/>
-      <c r="N213" s="1"/>
-      <c r="O213" s="1"/>
-      <c r="P213" s="1"/>
-      <c r="Q213" s="1"/>
-      <c r="R213" s="1"/>
-      <c r="S213" s="1"/>
-      <c r="T213" s="1"/>
-      <c r="U213" s="1"/>
-      <c r="V213" s="1"/>
-      <c r="W213" s="1"/>
-      <c r="X213" s="1"/>
-      <c r="Y213" s="1"/>
-    </row>
-    <row r="214" ht="15.0" customHeight="1">
-      <c r="A214" s="1"/>
-      <c r="B214" s="1"/>
-      <c r="C214" s="1"/>
-      <c r="D214" s="1"/>
-      <c r="E214" s="1"/>
-      <c r="F214" s="1"/>
-      <c r="G214" s="1"/>
-      <c r="H214" s="1"/>
-      <c r="I214" s="1"/>
-      <c r="J214" s="1"/>
-      <c r="K214" s="1"/>
-      <c r="L214" s="1"/>
-      <c r="M214" s="1"/>
-      <c r="N214" s="1"/>
-      <c r="O214" s="1"/>
-      <c r="P214" s="1"/>
-      <c r="Q214" s="1"/>
-      <c r="R214" s="1"/>
-      <c r="S214" s="1"/>
-      <c r="T214" s="1"/>
-      <c r="U214" s="1"/>
-      <c r="V214" s="1"/>
-      <c r="W214" s="1"/>
-      <c r="X214" s="1"/>
-      <c r="Y214" s="1"/>
-    </row>
-    <row r="215" ht="15.0" customHeight="1">
-      <c r="A215" s="1"/>
-      <c r="B215" s="1"/>
-      <c r="C215" s="1"/>
-      <c r="D215" s="1"/>
-      <c r="E215" s="1"/>
-      <c r="F215" s="1"/>
-      <c r="G215" s="1"/>
-      <c r="H215" s="1"/>
-      <c r="I215" s="1"/>
-      <c r="J215" s="1"/>
-      <c r="K215" s="1"/>
-      <c r="L215" s="1"/>
-      <c r="M215" s="1"/>
-      <c r="N215" s="1"/>
-      <c r="O215" s="1"/>
-      <c r="P215" s="1"/>
-      <c r="Q215" s="1"/>
-      <c r="R215" s="1"/>
-      <c r="S215" s="1"/>
-      <c r="T215" s="1"/>
-      <c r="U215" s="1"/>
-      <c r="V215" s="1"/>
-      <c r="W215" s="1"/>
-      <c r="X215" s="1"/>
-      <c r="Y215" s="1"/>
-    </row>
-    <row r="216" ht="15.0" customHeight="1">
-      <c r="A216" s="1"/>
-      <c r="B216" s="1"/>
-      <c r="C216" s="1"/>
-      <c r="D216" s="1"/>
-      <c r="E216" s="1"/>
-      <c r="F216" s="1"/>
-      <c r="G216" s="1"/>
-      <c r="H216" s="1"/>
-      <c r="I216" s="1"/>
-      <c r="J216" s="1"/>
-      <c r="K216" s="1"/>
-      <c r="L216" s="1"/>
-      <c r="M216" s="1"/>
-      <c r="N216" s="1"/>
-      <c r="O216" s="1"/>
-      <c r="P216" s="1"/>
-      <c r="Q216" s="1"/>
-      <c r="R216" s="1"/>
-      <c r="S216" s="1"/>
-      <c r="T216" s="1"/>
-      <c r="U216" s="1"/>
-      <c r="V216" s="1"/>
-      <c r="W216" s="1"/>
-      <c r="X216" s="1"/>
-      <c r="Y216" s="1"/>
-    </row>
-    <row r="217" ht="15.0" customHeight="1">
-      <c r="A217" s="1"/>
-      <c r="B217" s="1"/>
-      <c r="C217" s="1"/>
-      <c r="D217" s="1"/>
-      <c r="E217" s="1"/>
-      <c r="F217" s="1"/>
-      <c r="G217" s="1"/>
-      <c r="H217" s="1"/>
-      <c r="I217" s="1"/>
-      <c r="J217" s="1"/>
-      <c r="K217" s="1"/>
-      <c r="L217" s="1"/>
-      <c r="M217" s="1"/>
-      <c r="N217" s="1"/>
-      <c r="O217" s="1"/>
-      <c r="P217" s="1"/>
-      <c r="Q217" s="1"/>
-      <c r="R217" s="1"/>
-      <c r="S217" s="1"/>
-      <c r="T217" s="1"/>
-      <c r="U217" s="1"/>
-      <c r="V217" s="1"/>
-      <c r="W217" s="1"/>
-      <c r="X217" s="1"/>
-      <c r="Y217" s="1"/>
-    </row>
-    <row r="218" ht="15.0" customHeight="1">
-      <c r="A218" s="1"/>
-      <c r="B218" s="1"/>
-      <c r="C218" s="1"/>
-      <c r="D218" s="1"/>
-      <c r="E218" s="1"/>
-      <c r="F218" s="1"/>
-      <c r="G218" s="1"/>
-      <c r="H218" s="1"/>
-      <c r="I218" s="1"/>
-      <c r="J218" s="1"/>
-      <c r="K218" s="1"/>
-      <c r="L218" s="1"/>
-      <c r="M218" s="1"/>
-      <c r="N218" s="1"/>
-      <c r="O218" s="1"/>
-      <c r="P218" s="1"/>
-      <c r="Q218" s="1"/>
-      <c r="R218" s="1"/>
-      <c r="S218" s="1"/>
-      <c r="T218" s="1"/>
-      <c r="U218" s="1"/>
-      <c r="V218" s="1"/>
-      <c r="W218" s="1"/>
-      <c r="X218" s="1"/>
-      <c r="Y218" s="1"/>
-    </row>
-    <row r="219" ht="15.0" customHeight="1">
-      <c r="A219" s="1"/>
-      <c r="B219" s="1"/>
-      <c r="C219" s="1"/>
-      <c r="D219" s="1"/>
-      <c r="E219" s="1"/>
-      <c r="F219" s="1"/>
-      <c r="G219" s="1"/>
-      <c r="H219" s="1"/>
-      <c r="I219" s="1"/>
-      <c r="J219" s="1"/>
-      <c r="K219" s="1"/>
-      <c r="L219" s="1"/>
-      <c r="M219" s="1"/>
-      <c r="N219" s="1"/>
-      <c r="O219" s="1"/>
-      <c r="P219" s="1"/>
-      <c r="Q219" s="1"/>
-      <c r="R219" s="1"/>
-      <c r="S219" s="1"/>
-      <c r="T219" s="1"/>
-      <c r="U219" s="1"/>
-      <c r="V219" s="1"/>
-      <c r="W219" s="1"/>
-      <c r="X219" s="1"/>
-      <c r="Y219" s="1"/>
-    </row>
-    <row r="220" ht="15.0" customHeight="1">
-      <c r="A220" s="1"/>
-      <c r="B220" s="1"/>
-      <c r="C220" s="1"/>
-      <c r="D220" s="1"/>
-      <c r="E220" s="1"/>
-      <c r="F220" s="1"/>
-      <c r="G220" s="1"/>
-      <c r="H220" s="1"/>
-      <c r="I220" s="1"/>
-      <c r="J220" s="1"/>
-      <c r="K220" s="1"/>
-      <c r="L220" s="1"/>
-      <c r="M220" s="1"/>
-      <c r="N220" s="1"/>
-      <c r="O220" s="1"/>
-      <c r="P220" s="1"/>
-      <c r="Q220" s="1"/>
-      <c r="R220" s="1"/>
-      <c r="S220" s="1"/>
-      <c r="T220" s="1"/>
-      <c r="U220" s="1"/>
-      <c r="V220" s="1"/>
-      <c r="W220" s="1"/>
-      <c r="X220" s="1"/>
-      <c r="Y220" s="1"/>
-    </row>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
     <row r="221" ht="15.75" customHeight="1"/>
     <row r="222" ht="15.75" customHeight="1"/>
     <row r="223" ht="15.75" customHeight="1"/>
@@ -7302,14 +7002,6 @@
     <row r="990" ht="15.75" customHeight="1"/>
     <row r="991" ht="15.75" customHeight="1"/>
     <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Templates/Tables/ValueInfo/T_ValTable.xlsx
+++ b/Templates/Tables/ValueInfo/T_ValTable.xlsx
@@ -34,7 +34,7 @@
     <t>광고 딜레이</t>
   </si>
   <si>
-    <t>DELTA_TIME_ADS</t>
+    <t>DELTA_T_ADS</t>
   </si>
   <si>
     <t>광고 시간 간격</t>
@@ -167,19 +167,31 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -447,8 +459,8 @@
       <c r="C2" s="3">
         <v>60.0</v>
       </c>
-      <c r="D2" s="3">
-        <v>2.0</v>
+      <c r="D2" s="4">
+        <v>1.0</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>6</v>
@@ -473,273 +485,273 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
-      <c r="Z2" s="4"/>
+      <c r="Z2" s="5"/>
     </row>
     <row r="3" ht="15.0" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="7">
         <v>0.0</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="7">
         <v>10.0</v>
       </c>
-      <c r="D3" s="6">
-        <v>2.0</v>
+      <c r="D3" s="8">
+        <v>1.0</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="9"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>0.0</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="7">
         <v>6.0</v>
       </c>
-      <c r="D4" s="6">
-        <v>1.0</v>
+      <c r="D4" s="8">
+        <v>0.0</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="9"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>0.0</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="7">
         <v>0.0</v>
       </c>
-      <c r="D5" s="6">
-        <v>1.0</v>
+      <c r="D5" s="8">
+        <v>0.0</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="9"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>0.0</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="7">
         <v>60.0</v>
       </c>
-      <c r="D6" s="6">
-        <v>1.0</v>
+      <c r="D6" s="8">
+        <v>0.0</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="9"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>0.0</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <v>60.0</v>
       </c>
-      <c r="D7" s="6">
-        <v>1.0</v>
+      <c r="D7" s="8">
+        <v>0.0</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="9"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>0.0</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7">
         <v>60.0</v>
       </c>
-      <c r="D8" s="6">
-        <v>1.0</v>
+      <c r="D8" s="8">
+        <v>0.0</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="9"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="12">
         <v>0.0</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="12">
         <v>60.0</v>
       </c>
-      <c r="D9" s="9">
-        <v>1.0</v>
+      <c r="D9" s="13">
+        <v>0.0</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="9"/>
-      <c r="Z9" s="10"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="12"/>
+      <c r="V9" s="12"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="12"/>
+      <c r="Y9" s="12"/>
+      <c r="Z9" s="14"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1"/>
